--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL314"/>
+  <dimension ref="A1:BL332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64027,15 +64027,11 @@
           <t>31 977</t>
         </is>
       </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G314" t="n">
+        <v>1</v>
+      </c>
+      <c r="H314" t="n">
+        <v>1</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
@@ -64057,15 +64053,11 @@
           <t>Tottenham</t>
         </is>
       </c>
-      <c r="M314" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
-      <c r="N314" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
+      <c r="M314" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N314" t="n">
+        <v>0.98</v>
       </c>
       <c r="O314" t="inlineStr">
         <is>
@@ -64077,155 +64069,95 @@
           <t>73%</t>
         </is>
       </c>
-      <c r="Q314" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R314" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S314" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T314" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U314" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V314" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W314" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="X314" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y314" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z314" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA314" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB314" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC314" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AD314" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AE314" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AF314" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG314" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH314" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI314" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ314" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK314" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="AL314" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="AM314" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AN314" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AO314" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="AP314" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="AQ314" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AR314" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="AS314" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AT314" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="Q314" t="n">
+        <v>7</v>
+      </c>
+      <c r="R314" t="n">
+        <v>15</v>
+      </c>
+      <c r="S314" t="n">
+        <v>3</v>
+      </c>
+      <c r="T314" t="n">
+        <v>6</v>
+      </c>
+      <c r="U314" t="n">
+        <v>3</v>
+      </c>
+      <c r="V314" t="n">
+        <v>3</v>
+      </c>
+      <c r="W314" t="n">
+        <v>13</v>
+      </c>
+      <c r="X314" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y314" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z314" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA314" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB314" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC314" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD314" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE314" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF314" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG314" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH314" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI314" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ314" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK314" t="n">
+        <v>294</v>
+      </c>
+      <c r="AL314" t="n">
+        <v>719</v>
+      </c>
+      <c r="AM314" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN314" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO314" t="n">
+        <v>66</v>
+      </c>
+      <c r="AP314" t="n">
+        <v>102</v>
+      </c>
+      <c r="AQ314" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR314" t="n">
+        <v>88</v>
+      </c>
+      <c r="AS314" t="n">
+        <v>39</v>
+      </c>
+      <c r="AT314" t="n">
+        <v>16</v>
       </c>
       <c r="AU314" t="inlineStr">
         <is>
@@ -64261,15 +64193,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC314" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD314" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="BC314" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD314" t="n">
+        <v>6</v>
       </c>
       <c r="BE314" t="inlineStr"/>
       <c r="BF314" t="inlineStr"/>
@@ -64280,6 +64208,4710 @@
       <c r="BK314" t="inlineStr"/>
       <c r="BL314" t="inlineStr"/>
     </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2g67Vsyf</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>24.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Oliver M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Villa Park
+ (Birmingham)</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>42 789</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC315" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AD315" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AE315" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF315" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG315" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH315" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ315" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK315" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="AL315" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="AM315" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AN315" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AO315" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AP315" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AQ315" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AR315" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AS315" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT315" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU315" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="AV315" t="inlineStr">
+        <is>
+          <t>emery unai</t>
+        </is>
+      </c>
+      <c r="AW315" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="AX315" t="inlineStr">
+        <is>
+          <t>arteta mikel</t>
+        </is>
+      </c>
+      <c r="AY315" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ315" t="n">
+        <v>481</v>
+      </c>
+      <c r="BA315" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB315" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC315" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BD315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE315" t="inlineStr"/>
+      <c r="BF315" t="inlineStr"/>
+      <c r="BG315" t="inlineStr"/>
+      <c r="BH315" t="inlineStr"/>
+      <c r="BI315" t="inlineStr"/>
+      <c r="BJ315" t="inlineStr"/>
+      <c r="BK315" t="inlineStr"/>
+      <c r="BL315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>U5cORazJ</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>24.08.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Jones R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Selhurst Park
+ (London)</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>25 486</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>22 099</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>West Ham</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB316" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC316" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD316" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF316" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG316" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH316" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AI316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK316" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AL316" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="AM316" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AN316" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AO316" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="AP316" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AQ316" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AR316" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AS316" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AT316" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AU316" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="AV316" t="inlineStr">
+        <is>
+          <t>glasner oliver</t>
+        </is>
+      </c>
+      <c r="AW316" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="AX316" t="inlineStr">
+        <is>
+          <t>lopetegui julen</t>
+        </is>
+      </c>
+      <c r="AY316" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ316" t="n">
+        <v>481</v>
+      </c>
+      <c r="BA316" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB316" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC316" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BD316" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BE316" t="inlineStr"/>
+      <c r="BF316" t="inlineStr"/>
+      <c r="BG316" t="inlineStr"/>
+      <c r="BH316" t="inlineStr"/>
+      <c r="BI316" t="inlineStr"/>
+      <c r="BJ316" t="inlineStr"/>
+      <c r="BK316" t="inlineStr"/>
+      <c r="BL316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>dCkAk3SP</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>24.08.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Bond D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Craven Cottage
+ (London)</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>26 600</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>25 401</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Leicester</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE317" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF317" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG317" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AH317" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI317" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ317" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK317" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="AL317" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="AM317" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AN317" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AO317" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="AP317" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AQ317" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AR317" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AS317" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AT317" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AU317" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="AV317" t="inlineStr">
+        <is>
+          <t>silva marco</t>
+        </is>
+      </c>
+      <c r="AW317" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="AX317" t="inlineStr">
+        <is>
+          <t>cooper steven</t>
+        </is>
+      </c>
+      <c r="AY317" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ317" t="n">
+        <v>481</v>
+      </c>
+      <c r="BA317" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB317" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC317" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BD317" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BE317" t="inlineStr"/>
+      <c r="BF317" t="inlineStr"/>
+      <c r="BG317" t="inlineStr"/>
+      <c r="BH317" t="inlineStr"/>
+      <c r="BI317" t="inlineStr"/>
+      <c r="BJ317" t="inlineStr"/>
+      <c r="BK317" t="inlineStr"/>
+      <c r="BL317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>lAUlrLKa</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>24.08.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Allison S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Etihad Stadium
+ (Manchester)</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>55 097</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Ipswich</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD318" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AE318" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF318" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG318" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH318" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI318" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ318" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK318" t="inlineStr">
+        <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="AL318" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="AM318" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AN318" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AO318" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="AP318" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AQ318" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AR318" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AS318" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AT318" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AU318" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="AV318" t="inlineStr">
+        <is>
+          <t>guardiola pep</t>
+        </is>
+      </c>
+      <c r="AW318" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="AX318" t="inlineStr">
+        <is>
+          <t>mckenna kieran</t>
+        </is>
+      </c>
+      <c r="AY318" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ318" t="n">
+        <v>481</v>
+      </c>
+      <c r="BA318" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB318" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC318" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BD318" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE318" t="inlineStr"/>
+      <c r="BF318" t="inlineStr"/>
+      <c r="BG318" t="inlineStr"/>
+      <c r="BH318" t="inlineStr"/>
+      <c r="BI318" t="inlineStr"/>
+      <c r="BJ318" t="inlineStr"/>
+      <c r="BK318" t="inlineStr"/>
+      <c r="BL318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>fNaktakC</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>24.08.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Barrott S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>St. Mary's Stadium
+ (Southampton)</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>32 384</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>31 150</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD319" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF319" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI319" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ319" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK319" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="AL319" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="AM319" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AN319" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AO319" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AP319" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AQ319" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AR319" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AS319" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AT319" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AU319" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="AV319" t="inlineStr">
+        <is>
+          <t>martin russell</t>
+        </is>
+      </c>
+      <c r="AW319" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="AX319" t="inlineStr">
+        <is>
+          <t>espirito santo</t>
+        </is>
+      </c>
+      <c r="AY319" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ319" t="n">
+        <v>481</v>
+      </c>
+      <c r="BA319" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB319" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC319" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BD319" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BE319" t="inlineStr"/>
+      <c r="BF319" t="inlineStr"/>
+      <c r="BG319" t="inlineStr"/>
+      <c r="BH319" t="inlineStr"/>
+      <c r="BI319" t="inlineStr"/>
+      <c r="BJ319" t="inlineStr"/>
+      <c r="BK319" t="inlineStr"/>
+      <c r="BL319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2m3cvwKO</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>24.08.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Taylor A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>62 850</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>61 357</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC320" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD320" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE320" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF320" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG320" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH320" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI320" t="inlineStr"/>
+      <c r="AJ320" t="inlineStr"/>
+      <c r="AK320" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="AL320" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="AM320" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AN320" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AO320" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AP320" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AQ320" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AR320" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AS320" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AT320" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AU320" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="AV320" t="inlineStr">
+        <is>
+          <t>postecoglou ange</t>
+        </is>
+      </c>
+      <c r="AW320" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="AX320" t="inlineStr">
+        <is>
+          <t>dyche sean</t>
+        </is>
+      </c>
+      <c r="AY320" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ320" t="n">
+        <v>481</v>
+      </c>
+      <c r="BA320" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB320" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC320" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BD320" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BE320" t="inlineStr"/>
+      <c r="BF320" t="inlineStr"/>
+      <c r="BG320" t="inlineStr"/>
+      <c r="BH320" t="inlineStr"/>
+      <c r="BI320" t="inlineStr"/>
+      <c r="BJ320" t="inlineStr"/>
+      <c r="BK320" t="inlineStr"/>
+      <c r="BL320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>8j9FTL56</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>24.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Pawson C.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Amex Stadium
+ (Brighton)</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>31 876</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>31 537</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Manchester Utd</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE321" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF321" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG321" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI321" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ321" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK321" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="AL321" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="AM321" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AN321" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AO321" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="AP321" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AQ321" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="AR321" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AS321" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AT321" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU321" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="AV321" t="inlineStr">
+        <is>
+          <t>hurzeler fabian</t>
+        </is>
+      </c>
+      <c r="AW321" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="AX321" t="inlineStr">
+        <is>
+          <t>ten hag erik</t>
+        </is>
+      </c>
+      <c r="AY321" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ321" t="n">
+        <v>481</v>
+      </c>
+      <c r="BA321" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB321" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC321" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD321" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BE321" t="inlineStr"/>
+      <c r="BF321" t="inlineStr"/>
+      <c r="BG321" t="inlineStr"/>
+      <c r="BH321" t="inlineStr"/>
+      <c r="BI321" t="inlineStr"/>
+      <c r="BJ321" t="inlineStr"/>
+      <c r="BK321" t="inlineStr"/>
+      <c r="BL321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>23e0sUpB</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>24.08.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Smith L.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Ewood Park
+ (Blackburn)</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>31 367</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>14 769</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>Blackburn</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>vgOBT43c</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Oxford Utd</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W322" t="inlineStr"/>
+      <c r="X322" t="inlineStr"/>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AD322" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE322" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF322" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG322" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH322" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI322" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ322" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK322" t="inlineStr"/>
+      <c r="AL322" t="inlineStr"/>
+      <c r="AM322" t="inlineStr"/>
+      <c r="AN322" t="inlineStr"/>
+      <c r="AO322" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AP322" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="AQ322" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AR322" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AS322" t="inlineStr"/>
+      <c r="AT322" t="inlineStr"/>
+      <c r="AU322" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+      <c r="AV322" t="inlineStr">
+        <is>
+          <t>eustace john</t>
+        </is>
+      </c>
+      <c r="AW322" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
+      <c r="AX322" t="inlineStr">
+        <is>
+          <t>buckingham des</t>
+        </is>
+      </c>
+      <c r="AY322" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ322" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA322" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB322" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC322" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BD322" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BE322" t="inlineStr"/>
+      <c r="BF322" t="inlineStr"/>
+      <c r="BG322" t="inlineStr"/>
+      <c r="BH322" t="inlineStr"/>
+      <c r="BI322" t="inlineStr"/>
+      <c r="BJ322" t="inlineStr"/>
+      <c r="BK322" t="inlineStr"/>
+      <c r="BL322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>prkJckVi</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>24.08.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Donohue M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Riverside Stadium
+ (Middlesbrough)</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>34 742</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>26 270</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>6F0lvLNC</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>zckREQFJ</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W323" t="inlineStr"/>
+      <c r="X323" t="inlineStr"/>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AD323" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE323" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF323" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG323" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH323" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI323" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ323" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK323" t="inlineStr"/>
+      <c r="AL323" t="inlineStr"/>
+      <c r="AM323" t="inlineStr"/>
+      <c r="AN323" t="inlineStr"/>
+      <c r="AO323" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="AP323" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AQ323" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AR323" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AS323" t="inlineStr"/>
+      <c r="AT323" t="inlineStr"/>
+      <c r="AU323" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
+      <c r="AV323" t="inlineStr">
+        <is>
+          <t>carrick michael</t>
+        </is>
+      </c>
+      <c r="AW323" t="inlineStr">
+        <is>
+          <t>djl0V3o6</t>
+        </is>
+      </c>
+      <c r="AX323" t="inlineStr">
+        <is>
+          <t>mousinho john</t>
+        </is>
+      </c>
+      <c r="AY323" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ323" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA323" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB323" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC323" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BD323" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE323" t="inlineStr"/>
+      <c r="BF323" t="inlineStr"/>
+      <c r="BG323" t="inlineStr"/>
+      <c r="BH323" t="inlineStr"/>
+      <c r="BI323" t="inlineStr"/>
+      <c r="BJ323" t="inlineStr"/>
+      <c r="BK323" t="inlineStr"/>
+      <c r="BL323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>6cwSeTa4</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>24.08.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Smith J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Carrow Road
+ (Norwich)</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>27 137</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>26 373</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>Norwich</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Sheffield Utd</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W324" t="inlineStr"/>
+      <c r="X324" t="inlineStr"/>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC324" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AD324" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AE324" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF324" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI324" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ324" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK324" t="inlineStr"/>
+      <c r="AL324" t="inlineStr"/>
+      <c r="AM324" t="inlineStr"/>
+      <c r="AN324" t="inlineStr"/>
+      <c r="AO324" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AP324" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AQ324" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AR324" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AS324" t="inlineStr"/>
+      <c r="AT324" t="inlineStr"/>
+      <c r="AU324" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="AV324" t="inlineStr">
+        <is>
+          <t>thorup johannes</t>
+        </is>
+      </c>
+      <c r="AW324" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="AX324" t="inlineStr">
+        <is>
+          <t>wilder chris</t>
+        </is>
+      </c>
+      <c r="AY324" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ324" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA324" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB324" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD324" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BE324" t="inlineStr"/>
+      <c r="BF324" t="inlineStr"/>
+      <c r="BG324" t="inlineStr"/>
+      <c r="BH324" t="inlineStr"/>
+      <c r="BI324" t="inlineStr"/>
+      <c r="BJ324" t="inlineStr"/>
+      <c r="BK324" t="inlineStr"/>
+      <c r="BL324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>ENtzf7UG</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>24.08.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Whitestone D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Deepdale
+ (Preston)</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>23 408</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>15 245</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>x8IDVcbi</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>Preston</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Luton</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr"/>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W325" t="inlineStr"/>
+      <c r="X325" t="inlineStr"/>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z325" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB325" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC325" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD325" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AE325" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF325" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG325" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AH325" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI325" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ325" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK325" t="inlineStr"/>
+      <c r="AL325" t="inlineStr"/>
+      <c r="AM325" t="inlineStr"/>
+      <c r="AN325" t="inlineStr"/>
+      <c r="AO325" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AP325" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AQ325" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AR325" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AS325" t="inlineStr"/>
+      <c r="AT325" t="inlineStr"/>
+      <c r="AU325" t="inlineStr">
+        <is>
+          <t>lGE8iEO1</t>
+        </is>
+      </c>
+      <c r="AV325" t="inlineStr">
+        <is>
+          <t>heckingbottom paul</t>
+        </is>
+      </c>
+      <c r="AW325" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="AX325" t="inlineStr">
+        <is>
+          <t>edwards rob</t>
+        </is>
+      </c>
+      <c r="AY325" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ325" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA325" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB325" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC325" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BD325" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BE325" t="inlineStr"/>
+      <c r="BF325" t="inlineStr"/>
+      <c r="BG325" t="inlineStr"/>
+      <c r="BH325" t="inlineStr"/>
+      <c r="BI325" t="inlineStr"/>
+      <c r="BJ325" t="inlineStr"/>
+      <c r="BK325" t="inlineStr"/>
+      <c r="BL325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>6BI0ASEc</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>24.08.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Bell J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Bet365 Stadium
+ (Stoke on Trent)</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>30 089</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>24 371</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>hSUajdSS</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>Stoke</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>CCBWpzjj</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>West Brom</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr"/>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W326" t="inlineStr"/>
+      <c r="X326" t="inlineStr"/>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z326" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB326" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC326" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD326" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE326" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF326" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG326" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH326" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI326" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ326" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK326" t="inlineStr"/>
+      <c r="AL326" t="inlineStr"/>
+      <c r="AM326" t="inlineStr"/>
+      <c r="AN326" t="inlineStr"/>
+      <c r="AO326" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="AP326" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AQ326" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AR326" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AS326" t="inlineStr"/>
+      <c r="AT326" t="inlineStr"/>
+      <c r="AU326" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="AV326" t="inlineStr">
+        <is>
+          <t>schumacher steven</t>
+        </is>
+      </c>
+      <c r="AW326" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="AX326" t="inlineStr">
+        <is>
+          <t>corberan carlos</t>
+        </is>
+      </c>
+      <c r="AY326" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ326" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA326" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB326" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC326" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BD326" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BE326" t="inlineStr"/>
+      <c r="BF326" t="inlineStr"/>
+      <c r="BG326" t="inlineStr"/>
+      <c r="BH326" t="inlineStr"/>
+      <c r="BI326" t="inlineStr"/>
+      <c r="BJ326" t="inlineStr"/>
+      <c r="BK326" t="inlineStr"/>
+      <c r="BL326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>EyM886qA</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>24.08.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Martin S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Stadium of Light
+ (Sunderland)</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>48 707</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>40 096</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr"/>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr"/>
+      <c r="X327" t="inlineStr"/>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB327" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC327" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD327" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AE327" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF327" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AI327" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ327" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK327" t="inlineStr"/>
+      <c r="AL327" t="inlineStr"/>
+      <c r="AM327" t="inlineStr"/>
+      <c r="AN327" t="inlineStr"/>
+      <c r="AO327" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AP327" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AQ327" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AR327" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AS327" t="inlineStr"/>
+      <c r="AT327" t="inlineStr"/>
+      <c r="AU327" t="inlineStr">
+        <is>
+          <t>pYaUUJs1</t>
+        </is>
+      </c>
+      <c r="AV327" t="inlineStr">
+        <is>
+          <t>le bris regis</t>
+        </is>
+      </c>
+      <c r="AW327" t="inlineStr">
+        <is>
+          <t>YuNX1zGT</t>
+        </is>
+      </c>
+      <c r="AX327" t="inlineStr">
+        <is>
+          <t>parker scott</t>
+        </is>
+      </c>
+      <c r="AY327" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ327" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA327" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB327" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC327" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BD327" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE327" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF327" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BG327" t="inlineStr"/>
+      <c r="BH327" t="inlineStr"/>
+      <c r="BI327" t="inlineStr"/>
+      <c r="BJ327" t="inlineStr"/>
+      <c r="BK327" t="inlineStr"/>
+      <c r="BL327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>YPYtjbTr</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>24.08.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Eltringham G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Vicarage Road
+ (Watford)</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>22 200</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Iug0YO0Q</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Derby</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr"/>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W328" t="inlineStr"/>
+      <c r="X328" t="inlineStr"/>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z328" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB328" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC328" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AD328" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AE328" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF328" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG328" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH328" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI328" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ328" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK328" t="inlineStr"/>
+      <c r="AL328" t="inlineStr"/>
+      <c r="AM328" t="inlineStr"/>
+      <c r="AN328" t="inlineStr"/>
+      <c r="AO328" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="AP328" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="AQ328" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AR328" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AS328" t="inlineStr"/>
+      <c r="AT328" t="inlineStr"/>
+      <c r="AU328" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="AV328" t="inlineStr">
+        <is>
+          <t>cleverley tom</t>
+        </is>
+      </c>
+      <c r="AW328" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
+      <c r="AX328" t="inlineStr">
+        <is>
+          <t>warne paul</t>
+        </is>
+      </c>
+      <c r="AY328" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ328" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA328" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB328" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC328" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BD328" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BE328" t="inlineStr"/>
+      <c r="BF328" t="inlineStr"/>
+      <c r="BG328" t="inlineStr"/>
+      <c r="BH328" t="inlineStr"/>
+      <c r="BI328" t="inlineStr"/>
+      <c r="BJ328" t="inlineStr"/>
+      <c r="BK328" t="inlineStr"/>
+      <c r="BL328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>zHg8u8FN</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>24.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Kitchen A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Ashton Gate Stadium
+ (Bristol)</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>27 000</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>21 454</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>MahqU27I</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>Bristol City</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>GOvB22xg</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr"/>
+      <c r="X329" t="inlineStr"/>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB329" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC329" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AD329" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AE329" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF329" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AI329" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ329" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK329" t="inlineStr"/>
+      <c r="AL329" t="inlineStr"/>
+      <c r="AM329" t="inlineStr"/>
+      <c r="AN329" t="inlineStr"/>
+      <c r="AO329" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="AP329" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="AQ329" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AR329" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AS329" t="inlineStr"/>
+      <c r="AT329" t="inlineStr"/>
+      <c r="AU329" t="inlineStr">
+        <is>
+          <t>UwJevjpg</t>
+        </is>
+      </c>
+      <c r="AV329" t="inlineStr">
+        <is>
+          <t>manning liam</t>
+        </is>
+      </c>
+      <c r="AW329" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
+        </is>
+      </c>
+      <c r="AX329" t="inlineStr">
+        <is>
+          <t>robins mark</t>
+        </is>
+      </c>
+      <c r="AY329" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ329" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA329" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB329" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC329" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BD329" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BE329" t="inlineStr"/>
+      <c r="BF329" t="inlineStr"/>
+      <c r="BG329" t="inlineStr"/>
+      <c r="BH329" t="inlineStr"/>
+      <c r="BI329" t="inlineStr"/>
+      <c r="BJ329" t="inlineStr"/>
+      <c r="BK329" t="inlineStr"/>
+      <c r="BL329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>IycXZowo</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>24.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Webb D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>MKM Stadium
+ (Hull)</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>25 586</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>20 009</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>S66R0t75</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>Hull</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W330" t="inlineStr"/>
+      <c r="X330" t="inlineStr"/>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB330" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC330" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD330" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AE330" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF330" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG330" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH330" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI330" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ330" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK330" t="inlineStr"/>
+      <c r="AL330" t="inlineStr"/>
+      <c r="AM330" t="inlineStr"/>
+      <c r="AN330" t="inlineStr"/>
+      <c r="AO330" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AP330" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AQ330" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AR330" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AS330" t="inlineStr"/>
+      <c r="AT330" t="inlineStr"/>
+      <c r="AU330" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
+      <c r="AV330" t="inlineStr">
+        <is>
+          <t>walter tim</t>
+        </is>
+      </c>
+      <c r="AW330" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+      <c r="AX330" t="inlineStr">
+        <is>
+          <t>harris neil</t>
+        </is>
+      </c>
+      <c r="AY330" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ330" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA330" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB330" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC330" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BD330" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BE330" t="inlineStr"/>
+      <c r="BF330" t="inlineStr"/>
+      <c r="BG330" t="inlineStr"/>
+      <c r="BH330" t="inlineStr"/>
+      <c r="BI330" t="inlineStr"/>
+      <c r="BJ330" t="inlineStr"/>
+      <c r="BK330" t="inlineStr"/>
+      <c r="BL330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>fXlrhoaT</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>24.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Ward G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Loftus Road
+ (London)</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>18 439</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>15 285</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>QPR</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>WpGM6ELj</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Plymouth</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W331" t="inlineStr"/>
+      <c r="X331" t="inlineStr"/>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB331" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC331" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AD331" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AE331" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF331" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI331" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ331" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK331" t="inlineStr"/>
+      <c r="AL331" t="inlineStr"/>
+      <c r="AM331" t="inlineStr"/>
+      <c r="AN331" t="inlineStr"/>
+      <c r="AO331" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="AP331" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AQ331" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AR331" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AS331" t="inlineStr"/>
+      <c r="AT331" t="inlineStr"/>
+      <c r="AU331" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="AV331" t="inlineStr">
+        <is>
+          <t>cifuentes marti</t>
+        </is>
+      </c>
+      <c r="AW331" t="inlineStr">
+        <is>
+          <t>WfXv1DCa</t>
+        </is>
+      </c>
+      <c r="AX331" t="inlineStr">
+        <is>
+          <t>rooney wayne</t>
+        </is>
+      </c>
+      <c r="AY331" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ331" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA331" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB331" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC331" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BD331" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BE331" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF331" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BG331" t="inlineStr"/>
+      <c r="BH331" t="inlineStr"/>
+      <c r="BI331" t="inlineStr"/>
+      <c r="BJ331" t="inlineStr"/>
+      <c r="BK331" t="inlineStr"/>
+      <c r="BL331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>j3zEnPMj</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>23.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Hooper S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Hillsborough
+ (Sheffield)</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>39 732</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>28 800</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>llcCvIcG</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>Sheffield Wed</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr"/>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W332" t="inlineStr"/>
+      <c r="X332" t="inlineStr"/>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z332" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB332" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC332" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AD332" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE332" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF332" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG332" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH332" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI332" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ332" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK332" t="inlineStr"/>
+      <c r="AL332" t="inlineStr"/>
+      <c r="AM332" t="inlineStr"/>
+      <c r="AN332" t="inlineStr"/>
+      <c r="AO332" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AP332" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="AQ332" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AR332" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AS332" t="inlineStr"/>
+      <c r="AT332" t="inlineStr"/>
+      <c r="AU332" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+      <c r="AV332" t="inlineStr">
+        <is>
+          <t>rohl danny</t>
+        </is>
+      </c>
+      <c r="AW332" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="AX332" t="inlineStr">
+        <is>
+          <t>farke daniel</t>
+        </is>
+      </c>
+      <c r="AY332" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ332" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA332" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB332" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC332" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BD332" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BE332" t="inlineStr"/>
+      <c r="BF332" t="inlineStr"/>
+      <c r="BG332" t="inlineStr"/>
+      <c r="BH332" t="inlineStr"/>
+      <c r="BI332" t="inlineStr"/>
+      <c r="BJ332" t="inlineStr"/>
+      <c r="BK332" t="inlineStr"/>
+      <c r="BL332" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL332"/>
+  <dimension ref="A1:BL336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64237,15 +64237,11 @@
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G315" t="n">
+        <v>0</v>
+      </c>
+      <c r="H315" t="n">
+        <v>2</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
@@ -64267,15 +64263,11 @@
           <t>Arsenal</t>
         </is>
       </c>
-      <c r="M315" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="N315" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
+      <c r="M315" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="N315" t="n">
+        <v>1.34</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
@@ -64287,155 +64279,95 @@
           <t>57%</t>
         </is>
       </c>
-      <c r="Q315" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R315" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S315" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T315" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U315" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V315" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W315" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="X315" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y315" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA315" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC315" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AD315" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AE315" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF315" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG315" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH315" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AI315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ315" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK315" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="AL315" t="inlineStr">
-        <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="AM315" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AN315" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AO315" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AP315" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AQ315" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AR315" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="AS315" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT315" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q315" t="n">
+        <v>11</v>
+      </c>
+      <c r="R315" t="n">
+        <v>9</v>
+      </c>
+      <c r="S315" t="n">
+        <v>3</v>
+      </c>
+      <c r="T315" t="n">
+        <v>4</v>
+      </c>
+      <c r="U315" t="n">
+        <v>5</v>
+      </c>
+      <c r="V315" t="n">
+        <v>4</v>
+      </c>
+      <c r="W315" t="n">
+        <v>16</v>
+      </c>
+      <c r="X315" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y315" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z315" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA315" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB315" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC315" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD315" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE315" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF315" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG315" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH315" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI315" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ315" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK315" t="n">
+        <v>349</v>
+      </c>
+      <c r="AL315" t="n">
+        <v>546</v>
+      </c>
+      <c r="AM315" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN315" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO315" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP315" t="n">
+        <v>111</v>
+      </c>
+      <c r="AQ315" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR315" t="n">
+        <v>71</v>
+      </c>
+      <c r="AS315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT315" t="n">
+        <v>0</v>
       </c>
       <c r="AU315" t="inlineStr">
         <is>
@@ -64471,15 +64403,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC315" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BD315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC315" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD315" t="n">
+        <v>1</v>
       </c>
       <c r="BE315" t="inlineStr"/>
       <c r="BF315" t="inlineStr"/>
@@ -64523,15 +64451,11 @@
           <t>22 099</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G316" t="n">
+        <v>0</v>
+      </c>
+      <c r="H316" t="n">
+        <v>2</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
@@ -64553,15 +64477,11 @@
           <t>West Ham</t>
         </is>
       </c>
-      <c r="M316" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="N316" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
+      <c r="M316" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="N316" t="n">
+        <v>1.41</v>
       </c>
       <c r="O316" t="inlineStr">
         <is>
@@ -64573,155 +64493,95 @@
           <t>41%</t>
         </is>
       </c>
-      <c r="Q316" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R316" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T316" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U316" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V316" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W316" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="X316" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y316" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z316" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA316" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC316" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AD316" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AE316" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG316" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH316" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AI316" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ316" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK316" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="AL316" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="AM316" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AN316" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AO316" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="AP316" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AQ316" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AR316" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AS316" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AT316" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="Q316" t="n">
+        <v>14</v>
+      </c>
+      <c r="R316" t="n">
+        <v>18</v>
+      </c>
+      <c r="S316" t="n">
+        <v>2</v>
+      </c>
+      <c r="T316" t="n">
+        <v>3</v>
+      </c>
+      <c r="U316" t="n">
+        <v>8</v>
+      </c>
+      <c r="V316" t="n">
+        <v>10</v>
+      </c>
+      <c r="W316" t="n">
+        <v>19</v>
+      </c>
+      <c r="X316" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y316" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z316" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA316" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB316" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC316" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD316" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE316" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF316" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG316" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH316" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI316" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ316" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK316" t="n">
+        <v>549</v>
+      </c>
+      <c r="AL316" t="n">
+        <v>388</v>
+      </c>
+      <c r="AM316" t="n">
+        <v>23</v>
+      </c>
+      <c r="AN316" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO316" t="n">
+        <v>122</v>
+      </c>
+      <c r="AP316" t="n">
+        <v>96</v>
+      </c>
+      <c r="AQ316" t="n">
+        <v>52</v>
+      </c>
+      <c r="AR316" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS316" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT316" t="n">
+        <v>25</v>
       </c>
       <c r="AU316" t="inlineStr">
         <is>
@@ -64757,15 +64617,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC316" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BD316" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="BC316" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD316" t="n">
+        <v>5</v>
       </c>
       <c r="BE316" t="inlineStr"/>
       <c r="BF316" t="inlineStr"/>
@@ -64809,15 +64665,11 @@
           <t>25 401</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G317" t="n">
+        <v>2</v>
+      </c>
+      <c r="H317" t="n">
+        <v>1</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
@@ -64839,15 +64691,11 @@
           <t>Leicester</t>
         </is>
       </c>
-      <c r="M317" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="N317" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
+      <c r="M317" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N317" t="n">
+        <v>0.47</v>
       </c>
       <c r="O317" t="inlineStr">
         <is>
@@ -64859,155 +64707,95 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="Q317" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R317" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S317" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T317" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U317" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V317" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W317" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="X317" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Y317" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z317" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA317" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB317" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC317" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AD317" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AE317" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF317" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG317" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AH317" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AI317" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ317" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK317" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="AL317" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
-      </c>
-      <c r="AM317" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AN317" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AO317" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="AP317" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="AQ317" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="AR317" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AS317" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AT317" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="Q317" t="n">
+        <v>18</v>
+      </c>
+      <c r="R317" t="n">
+        <v>10</v>
+      </c>
+      <c r="S317" t="n">
+        <v>6</v>
+      </c>
+      <c r="T317" t="n">
+        <v>4</v>
+      </c>
+      <c r="U317" t="n">
+        <v>8</v>
+      </c>
+      <c r="V317" t="n">
+        <v>4</v>
+      </c>
+      <c r="W317" t="n">
+        <v>16</v>
+      </c>
+      <c r="X317" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y317" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z317" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB317" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC317" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD317" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE317" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF317" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG317" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH317" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI317" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ317" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK317" t="n">
+        <v>529</v>
+      </c>
+      <c r="AL317" t="n">
+        <v>427</v>
+      </c>
+      <c r="AM317" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN317" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO317" t="n">
+        <v>144</v>
+      </c>
+      <c r="AP317" t="n">
+        <v>63</v>
+      </c>
+      <c r="AQ317" t="n">
+        <v>67</v>
+      </c>
+      <c r="AR317" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS317" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT317" t="n">
+        <v>30</v>
       </c>
       <c r="AU317" t="inlineStr">
         <is>
@@ -65043,15 +64831,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC317" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BD317" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="BC317" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD317" t="n">
+        <v>2</v>
       </c>
       <c r="BE317" t="inlineStr"/>
       <c r="BF317" t="inlineStr"/>
@@ -65091,15 +64875,11 @@
         </is>
       </c>
       <c r="F318" t="inlineStr"/>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G318" t="n">
+        <v>4</v>
+      </c>
+      <c r="H318" t="n">
+        <v>1</v>
       </c>
       <c r="I318" t="inlineStr">
         <is>
@@ -65121,15 +64901,11 @@
           <t>Ipswich</t>
         </is>
       </c>
-      <c r="M318" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="N318" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
+      <c r="M318" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="N318" t="n">
+        <v>0.37</v>
       </c>
       <c r="O318" t="inlineStr">
         <is>
@@ -65141,155 +64917,95 @@
           <t>24%</t>
         </is>
       </c>
-      <c r="Q318" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R318" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S318" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T318" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U318" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V318" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W318" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="X318" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y318" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z318" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA318" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB318" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC318" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AD318" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AE318" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF318" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG318" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH318" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI318" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ318" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK318" t="inlineStr">
-        <is>
-          <t>749</t>
-        </is>
-      </c>
-      <c r="AL318" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="AM318" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AN318" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AO318" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="AP318" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AQ318" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AR318" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AS318" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AT318" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="Q318" t="n">
+        <v>14</v>
+      </c>
+      <c r="R318" t="n">
+        <v>2</v>
+      </c>
+      <c r="S318" t="n">
+        <v>5</v>
+      </c>
+      <c r="T318" t="n">
+        <v>2</v>
+      </c>
+      <c r="U318" t="n">
+        <v>4</v>
+      </c>
+      <c r="V318" t="n">
+        <v>0</v>
+      </c>
+      <c r="W318" t="n">
+        <v>16</v>
+      </c>
+      <c r="X318" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y318" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z318" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA318" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB318" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC318" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD318" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE318" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF318" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG318" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH318" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI318" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ318" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK318" t="n">
+        <v>749</v>
+      </c>
+      <c r="AL318" t="n">
+        <v>233</v>
+      </c>
+      <c r="AM318" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN318" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO318" t="n">
+        <v>131</v>
+      </c>
+      <c r="AP318" t="n">
+        <v>29</v>
+      </c>
+      <c r="AQ318" t="n">
+        <v>111</v>
+      </c>
+      <c r="AR318" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS318" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT318" t="n">
+        <v>40</v>
       </c>
       <c r="AU318" t="inlineStr">
         <is>
@@ -65325,15 +65041,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC318" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BD318" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BC318" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD318" t="n">
+        <v>0</v>
       </c>
       <c r="BE318" t="inlineStr"/>
       <c r="BF318" t="inlineStr"/>
@@ -65377,15 +65089,11 @@
           <t>31 150</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G319" t="n">
+        <v>0</v>
+      </c>
+      <c r="H319" t="n">
+        <v>1</v>
       </c>
       <c r="I319" t="inlineStr">
         <is>
@@ -65407,15 +65115,11 @@
           <t>Nottingham</t>
         </is>
       </c>
-      <c r="M319" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="N319" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
+      <c r="M319" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N319" t="n">
+        <v>2.14</v>
       </c>
       <c r="O319" t="inlineStr">
         <is>
@@ -65427,155 +65131,95 @@
           <t>35%</t>
         </is>
       </c>
-      <c r="Q319" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R319" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S319" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T319" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U319" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V319" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W319" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X319" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Y319" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z319" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA319" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB319" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC319" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AD319" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AE319" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AF319" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG319" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AH319" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AI319" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ319" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK319" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="AL319" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="AM319" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AN319" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AO319" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AP319" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="AQ319" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="AR319" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AS319" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AT319" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="Q319" t="n">
+        <v>5</v>
+      </c>
+      <c r="R319" t="n">
+        <v>23</v>
+      </c>
+      <c r="S319" t="n">
+        <v>1</v>
+      </c>
+      <c r="T319" t="n">
+        <v>8</v>
+      </c>
+      <c r="U319" t="n">
+        <v>1</v>
+      </c>
+      <c r="V319" t="n">
+        <v>8</v>
+      </c>
+      <c r="W319" t="n">
+        <v>15</v>
+      </c>
+      <c r="X319" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y319" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z319" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB319" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC319" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD319" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE319" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF319" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG319" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH319" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI319" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ319" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK319" t="n">
+        <v>641</v>
+      </c>
+      <c r="AL319" t="n">
+        <v>345</v>
+      </c>
+      <c r="AM319" t="n">
+        <v>18</v>
+      </c>
+      <c r="AN319" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO319" t="n">
+        <v>112</v>
+      </c>
+      <c r="AP319" t="n">
+        <v>73</v>
+      </c>
+      <c r="AQ319" t="n">
+        <v>41</v>
+      </c>
+      <c r="AR319" t="n">
+        <v>52</v>
+      </c>
+      <c r="AS319" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT319" t="n">
+        <v>24</v>
       </c>
       <c r="AU319" t="inlineStr">
         <is>
@@ -65611,15 +65255,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC319" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BD319" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="BC319" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD319" t="n">
+        <v>7</v>
       </c>
       <c r="BE319" t="inlineStr"/>
       <c r="BF319" t="inlineStr"/>
@@ -65663,15 +65303,11 @@
           <t>61 357</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G320" t="n">
+        <v>4</v>
+      </c>
+      <c r="H320" t="n">
+        <v>0</v>
       </c>
       <c r="I320" t="inlineStr">
         <is>
@@ -65693,15 +65329,11 @@
           <t>Everton</t>
         </is>
       </c>
-      <c r="M320" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
-      <c r="N320" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
+      <c r="M320" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="N320" t="n">
+        <v>0.48</v>
       </c>
       <c r="O320" t="inlineStr">
         <is>
@@ -65713,147 +65345,91 @@
           <t>29%</t>
         </is>
       </c>
-      <c r="Q320" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R320" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S320" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T320" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U320" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V320" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W320" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="X320" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y320" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z320" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA320" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB320" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC320" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD320" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE320" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF320" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG320" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH320" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="Q320" t="n">
+        <v>13</v>
+      </c>
+      <c r="R320" t="n">
+        <v>10</v>
+      </c>
+      <c r="S320" t="n">
+        <v>7</v>
+      </c>
+      <c r="T320" t="n">
+        <v>1</v>
+      </c>
+      <c r="U320" t="n">
+        <v>4</v>
+      </c>
+      <c r="V320" t="n">
+        <v>7</v>
+      </c>
+      <c r="W320" t="n">
+        <v>17</v>
+      </c>
+      <c r="X320" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y320" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z320" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA320" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB320" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC320" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD320" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE320" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF320" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG320" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH320" t="n">
+        <v>15</v>
       </c>
       <c r="AI320" t="inlineStr"/>
       <c r="AJ320" t="inlineStr"/>
-      <c r="AK320" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="AL320" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="AM320" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AN320" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AO320" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AP320" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="AQ320" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="AR320" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="AS320" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AT320" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="AK320" t="n">
+        <v>602</v>
+      </c>
+      <c r="AL320" t="n">
+        <v>242</v>
+      </c>
+      <c r="AM320" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN320" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO320" t="n">
+        <v>109</v>
+      </c>
+      <c r="AP320" t="n">
+        <v>72</v>
+      </c>
+      <c r="AQ320" t="n">
+        <v>67</v>
+      </c>
+      <c r="AR320" t="n">
+        <v>41</v>
+      </c>
+      <c r="AS320" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT320" t="n">
+        <v>15</v>
       </c>
       <c r="AU320" t="inlineStr">
         <is>
@@ -65889,15 +65465,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC320" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BD320" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="BC320" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD320" t="n">
+        <v>2</v>
       </c>
       <c r="BE320" t="inlineStr"/>
       <c r="BF320" t="inlineStr"/>
@@ -65941,15 +65513,11 @@
           <t>31 537</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G321" t="n">
+        <v>2</v>
+      </c>
+      <c r="H321" t="n">
+        <v>1</v>
       </c>
       <c r="I321" t="inlineStr">
         <is>
@@ -65971,15 +65539,11 @@
           <t>Manchester Utd</t>
         </is>
       </c>
-      <c r="M321" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="N321" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="M321" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="N321" t="n">
+        <v>1.65</v>
       </c>
       <c r="O321" t="inlineStr">
         <is>
@@ -65991,155 +65555,95 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q321" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R321" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S321" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T321" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U321" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V321" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W321" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="X321" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y321" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z321" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA321" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB321" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC321" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD321" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AE321" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF321" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG321" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH321" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AI321" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ321" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK321" t="inlineStr">
-        <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="AL321" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="AM321" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AN321" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AO321" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AP321" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="AQ321" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="AR321" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="AS321" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AT321" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="Q321" t="n">
+        <v>14</v>
+      </c>
+      <c r="R321" t="n">
+        <v>11</v>
+      </c>
+      <c r="S321" t="n">
+        <v>5</v>
+      </c>
+      <c r="T321" t="n">
+        <v>4</v>
+      </c>
+      <c r="U321" t="n">
+        <v>8</v>
+      </c>
+      <c r="V321" t="n">
+        <v>5</v>
+      </c>
+      <c r="W321" t="n">
+        <v>14</v>
+      </c>
+      <c r="X321" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y321" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z321" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA321" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB321" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC321" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD321" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE321" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF321" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG321" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH321" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI321" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ321" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK321" t="n">
+        <v>463</v>
+      </c>
+      <c r="AL321" t="n">
+        <v>507</v>
+      </c>
+      <c r="AM321" t="n">
+        <v>18</v>
+      </c>
+      <c r="AN321" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO321" t="n">
+        <v>77</v>
+      </c>
+      <c r="AP321" t="n">
+        <v>84</v>
+      </c>
+      <c r="AQ321" t="n">
+        <v>68</v>
+      </c>
+      <c r="AR321" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS321" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT321" t="n">
+        <v>10</v>
       </c>
       <c r="AU321" t="inlineStr">
         <is>
@@ -66175,15 +65679,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC321" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD321" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="BC321" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD321" t="n">
+        <v>2</v>
       </c>
       <c r="BE321" t="inlineStr"/>
       <c r="BF321" t="inlineStr"/>
@@ -66227,15 +65727,11 @@
           <t>14 769</t>
         </is>
       </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G322" t="n">
+        <v>2</v>
+      </c>
+      <c r="H322" t="n">
+        <v>1</v>
       </c>
       <c r="I322" t="inlineStr">
         <is>
@@ -66269,121 +65765,77 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q322" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R322" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S322" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T322" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U322" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V322" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Q322" t="n">
+        <v>21</v>
+      </c>
+      <c r="R322" t="n">
+        <v>14</v>
+      </c>
+      <c r="S322" t="n">
+        <v>4</v>
+      </c>
+      <c r="T322" t="n">
+        <v>3</v>
+      </c>
+      <c r="U322" t="n">
+        <v>8</v>
+      </c>
+      <c r="V322" t="n">
+        <v>6</v>
       </c>
       <c r="W322" t="inlineStr"/>
       <c r="X322" t="inlineStr"/>
-      <c r="Y322" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z322" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA322" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB322" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC322" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AD322" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AE322" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF322" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG322" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH322" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI322" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ322" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y322" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z322" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA322" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB322" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC322" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD322" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE322" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF322" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG322" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH322" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI322" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ322" t="n">
+        <v>1</v>
       </c>
       <c r="AK322" t="inlineStr"/>
       <c r="AL322" t="inlineStr"/>
       <c r="AM322" t="inlineStr"/>
       <c r="AN322" t="inlineStr"/>
-      <c r="AO322" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AP322" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="AQ322" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="AR322" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="AO322" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP322" t="n">
+        <v>127</v>
+      </c>
+      <c r="AQ322" t="n">
+        <v>66</v>
+      </c>
+      <c r="AR322" t="n">
+        <v>32</v>
       </c>
       <c r="AS322" t="inlineStr"/>
       <c r="AT322" t="inlineStr"/>
@@ -66421,15 +65873,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC322" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BD322" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="BC322" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD322" t="n">
+        <v>5</v>
       </c>
       <c r="BE322" t="inlineStr"/>
       <c r="BF322" t="inlineStr"/>
@@ -66473,15 +65921,11 @@
           <t>26 270</t>
         </is>
       </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G323" t="n">
+        <v>2</v>
+      </c>
+      <c r="H323" t="n">
+        <v>2</v>
       </c>
       <c r="I323" t="inlineStr">
         <is>
@@ -66515,121 +65959,77 @@
           <t>33%</t>
         </is>
       </c>
-      <c r="Q323" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R323" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S323" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T323" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U323" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V323" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q323" t="n">
+        <v>31</v>
+      </c>
+      <c r="R323" t="n">
+        <v>7</v>
+      </c>
+      <c r="S323" t="n">
+        <v>8</v>
+      </c>
+      <c r="T323" t="n">
+        <v>3</v>
+      </c>
+      <c r="U323" t="n">
+        <v>9</v>
+      </c>
+      <c r="V323" t="n">
+        <v>3</v>
       </c>
       <c r="W323" t="inlineStr"/>
       <c r="X323" t="inlineStr"/>
-      <c r="Y323" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z323" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA323" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB323" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC323" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AD323" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AE323" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF323" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG323" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH323" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI323" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ323" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y323" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z323" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA323" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB323" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC323" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD323" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE323" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF323" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG323" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH323" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ323" t="n">
+        <v>5</v>
       </c>
       <c r="AK323" t="inlineStr"/>
       <c r="AL323" t="inlineStr"/>
       <c r="AM323" t="inlineStr"/>
       <c r="AN323" t="inlineStr"/>
-      <c r="AO323" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="AP323" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="AQ323" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AR323" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="AO323" t="n">
+        <v>165</v>
+      </c>
+      <c r="AP323" t="n">
+        <v>72</v>
+      </c>
+      <c r="AQ323" t="n">
+        <v>106</v>
+      </c>
+      <c r="AR323" t="n">
+        <v>19</v>
       </c>
       <c r="AS323" t="inlineStr"/>
       <c r="AT323" t="inlineStr"/>
@@ -66667,15 +66067,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC323" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BD323" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC323" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD323" t="n">
+        <v>1</v>
       </c>
       <c r="BE323" t="inlineStr"/>
       <c r="BF323" t="inlineStr"/>
@@ -66719,15 +66115,11 @@
           <t>26 373</t>
         </is>
       </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G324" t="n">
+        <v>1</v>
+      </c>
+      <c r="H324" t="n">
+        <v>1</v>
       </c>
       <c r="I324" t="inlineStr">
         <is>
@@ -66761,121 +66153,77 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q324" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R324" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S324" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T324" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V324" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q324" t="n">
+        <v>7</v>
+      </c>
+      <c r="R324" t="n">
+        <v>12</v>
+      </c>
+      <c r="S324" t="n">
+        <v>5</v>
+      </c>
+      <c r="T324" t="n">
+        <v>4</v>
+      </c>
+      <c r="U324" t="n">
+        <v>1</v>
+      </c>
+      <c r="V324" t="n">
+        <v>4</v>
       </c>
       <c r="W324" t="inlineStr"/>
       <c r="X324" t="inlineStr"/>
-      <c r="Y324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z324" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC324" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AD324" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AE324" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF324" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG324" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AH324" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI324" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AJ324" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y324" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA324" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB324" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC324" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD324" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE324" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF324" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG324" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH324" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI324" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ324" t="n">
+        <v>2</v>
       </c>
       <c r="AK324" t="inlineStr"/>
       <c r="AL324" t="inlineStr"/>
       <c r="AM324" t="inlineStr"/>
       <c r="AN324" t="inlineStr"/>
-      <c r="AO324" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AP324" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AQ324" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="AR324" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+      <c r="AO324" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP324" t="n">
+        <v>106</v>
+      </c>
+      <c r="AQ324" t="n">
+        <v>46</v>
+      </c>
+      <c r="AR324" t="n">
+        <v>61</v>
       </c>
       <c r="AS324" t="inlineStr"/>
       <c r="AT324" t="inlineStr"/>
@@ -66913,15 +66261,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD324" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="BC324" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD324" t="n">
+        <v>4</v>
       </c>
       <c r="BE324" t="inlineStr"/>
       <c r="BF324" t="inlineStr"/>
@@ -66965,15 +66309,11 @@
           <t>15 245</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H325" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G325" t="n">
+        <v>1</v>
+      </c>
+      <c r="H325" t="n">
+        <v>0</v>
       </c>
       <c r="I325" t="inlineStr">
         <is>
@@ -67007,121 +66347,77 @@
           <t>57%</t>
         </is>
       </c>
-      <c r="Q325" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R325" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S325" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T325" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U325" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V325" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Q325" t="n">
+        <v>7</v>
+      </c>
+      <c r="R325" t="n">
+        <v>17</v>
+      </c>
+      <c r="S325" t="n">
+        <v>3</v>
+      </c>
+      <c r="T325" t="n">
+        <v>4</v>
+      </c>
+      <c r="U325" t="n">
+        <v>2</v>
+      </c>
+      <c r="V325" t="n">
+        <v>7</v>
       </c>
       <c r="W325" t="inlineStr"/>
       <c r="X325" t="inlineStr"/>
-      <c r="Y325" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z325" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA325" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB325" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC325" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AD325" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AE325" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF325" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG325" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AH325" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI325" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AJ325" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y325" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z325" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA325" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB325" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC325" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD325" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE325" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF325" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG325" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH325" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI325" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ325" t="n">
+        <v>1</v>
       </c>
       <c r="AK325" t="inlineStr"/>
       <c r="AL325" t="inlineStr"/>
       <c r="AM325" t="inlineStr"/>
       <c r="AN325" t="inlineStr"/>
-      <c r="AO325" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AP325" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AQ325" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AR325" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="AO325" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP325" t="n">
+        <v>125</v>
+      </c>
+      <c r="AQ325" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR325" t="n">
+        <v>63</v>
       </c>
       <c r="AS325" t="inlineStr"/>
       <c r="AT325" t="inlineStr"/>
@@ -67159,15 +66455,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC325" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BD325" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="BC325" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD325" t="n">
+        <v>6</v>
       </c>
       <c r="BE325" t="inlineStr"/>
       <c r="BF325" t="inlineStr"/>
@@ -67211,15 +66503,11 @@
           <t>24 371</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G326" t="n">
+        <v>1</v>
+      </c>
+      <c r="H326" t="n">
+        <v>2</v>
       </c>
       <c r="I326" t="inlineStr">
         <is>
@@ -67253,121 +66541,77 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q326" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R326" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S326" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T326" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U326" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V326" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q326" t="n">
+        <v>10</v>
+      </c>
+      <c r="R326" t="n">
+        <v>20</v>
+      </c>
+      <c r="S326" t="n">
+        <v>2</v>
+      </c>
+      <c r="T326" t="n">
+        <v>5</v>
+      </c>
+      <c r="U326" t="n">
+        <v>5</v>
+      </c>
+      <c r="V326" t="n">
+        <v>3</v>
       </c>
       <c r="W326" t="inlineStr"/>
       <c r="X326" t="inlineStr"/>
-      <c r="Y326" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z326" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA326" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB326" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC326" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AD326" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AE326" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF326" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG326" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH326" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI326" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ326" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y326" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z326" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA326" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB326" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC326" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD326" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE326" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF326" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG326" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH326" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI326" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ326" t="n">
+        <v>3</v>
       </c>
       <c r="AK326" t="inlineStr"/>
       <c r="AL326" t="inlineStr"/>
       <c r="AM326" t="inlineStr"/>
       <c r="AN326" t="inlineStr"/>
-      <c r="AO326" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="AP326" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="AQ326" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="AR326" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="AO326" t="n">
+        <v>124</v>
+      </c>
+      <c r="AP326" t="n">
+        <v>84</v>
+      </c>
+      <c r="AQ326" t="n">
+        <v>46</v>
+      </c>
+      <c r="AR326" t="n">
+        <v>35</v>
       </c>
       <c r="AS326" t="inlineStr"/>
       <c r="AT326" t="inlineStr"/>
@@ -67405,15 +66649,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC326" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BD326" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="BC326" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD326" t="n">
+        <v>12</v>
       </c>
       <c r="BE326" t="inlineStr"/>
       <c r="BF326" t="inlineStr"/>
@@ -67457,15 +66697,11 @@
           <t>40 096</t>
         </is>
       </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G327" t="n">
+        <v>1</v>
+      </c>
+      <c r="H327" t="n">
+        <v>0</v>
       </c>
       <c r="I327" t="inlineStr">
         <is>
@@ -67499,121 +66735,77 @@
           <t>61%</t>
         </is>
       </c>
-      <c r="Q327" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R327" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S327" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T327" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U327" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V327" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q327" t="n">
+        <v>15</v>
+      </c>
+      <c r="R327" t="n">
+        <v>4</v>
+      </c>
+      <c r="S327" t="n">
+        <v>3</v>
+      </c>
+      <c r="T327" t="n">
+        <v>1</v>
+      </c>
+      <c r="U327" t="n">
+        <v>6</v>
+      </c>
+      <c r="V327" t="n">
+        <v>2</v>
       </c>
       <c r="W327" t="inlineStr"/>
       <c r="X327" t="inlineStr"/>
-      <c r="Y327" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z327" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA327" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB327" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC327" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AD327" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AE327" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF327" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG327" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AH327" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AI327" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ327" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y327" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z327" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA327" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB327" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC327" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD327" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE327" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF327" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG327" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH327" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI327" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ327" t="n">
+        <v>3</v>
       </c>
       <c r="AK327" t="inlineStr"/>
       <c r="AL327" t="inlineStr"/>
       <c r="AM327" t="inlineStr"/>
       <c r="AN327" t="inlineStr"/>
-      <c r="AO327" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AP327" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AQ327" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AR327" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="AO327" t="n">
+        <v>96</v>
+      </c>
+      <c r="AP327" t="n">
+        <v>95</v>
+      </c>
+      <c r="AQ327" t="n">
+        <v>50</v>
+      </c>
+      <c r="AR327" t="n">
+        <v>16</v>
       </c>
       <c r="AS327" t="inlineStr"/>
       <c r="AT327" t="inlineStr"/>
@@ -67651,25 +66843,17 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC327" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BD327" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BE327" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF327" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BC327" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD327" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE327" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF327" t="n">
+        <v>0</v>
       </c>
       <c r="BG327" t="inlineStr"/>
       <c r="BH327" t="inlineStr"/>
@@ -67707,15 +66891,11 @@
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H328" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G328" t="n">
+        <v>2</v>
+      </c>
+      <c r="H328" t="n">
+        <v>1</v>
       </c>
       <c r="I328" t="inlineStr">
         <is>
@@ -67749,121 +66929,77 @@
           <t>32%</t>
         </is>
       </c>
-      <c r="Q328" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R328" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S328" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T328" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U328" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V328" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q328" t="n">
+        <v>12</v>
+      </c>
+      <c r="R328" t="n">
+        <v>9</v>
+      </c>
+      <c r="S328" t="n">
+        <v>3</v>
+      </c>
+      <c r="T328" t="n">
+        <v>3</v>
+      </c>
+      <c r="U328" t="n">
+        <v>6</v>
+      </c>
+      <c r="V328" t="n">
+        <v>3</v>
       </c>
       <c r="W328" t="inlineStr"/>
       <c r="X328" t="inlineStr"/>
-      <c r="Y328" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z328" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA328" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB328" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC328" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AD328" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AE328" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF328" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG328" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH328" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AI328" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ328" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y328" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z328" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA328" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB328" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC328" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD328" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE328" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF328" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG328" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH328" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI328" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ328" t="n">
+        <v>3</v>
       </c>
       <c r="AK328" t="inlineStr"/>
       <c r="AL328" t="inlineStr"/>
       <c r="AM328" t="inlineStr"/>
       <c r="AN328" t="inlineStr"/>
-      <c r="AO328" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="AP328" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="AQ328" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AR328" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="AO328" t="n">
+        <v>142</v>
+      </c>
+      <c r="AP328" t="n">
+        <v>89</v>
+      </c>
+      <c r="AQ328" t="n">
+        <v>70</v>
+      </c>
+      <c r="AR328" t="n">
+        <v>41</v>
       </c>
       <c r="AS328" t="inlineStr"/>
       <c r="AT328" t="inlineStr"/>
@@ -67901,15 +67037,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC328" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BD328" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="BC328" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD328" t="n">
+        <v>3</v>
       </c>
       <c r="BE328" t="inlineStr"/>
       <c r="BF328" t="inlineStr"/>
@@ -67953,15 +67085,11 @@
           <t>21 454</t>
         </is>
       </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G329" t="n">
+        <v>1</v>
+      </c>
+      <c r="H329" t="n">
+        <v>1</v>
       </c>
       <c r="I329" t="inlineStr">
         <is>
@@ -67995,121 +67123,77 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q329" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R329" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S329" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T329" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U329" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V329" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q329" t="n">
+        <v>13</v>
+      </c>
+      <c r="R329" t="n">
+        <v>9</v>
+      </c>
+      <c r="S329" t="n">
+        <v>8</v>
+      </c>
+      <c r="T329" t="n">
+        <v>1</v>
+      </c>
+      <c r="U329" t="n">
+        <v>2</v>
+      </c>
+      <c r="V329" t="n">
+        <v>5</v>
       </c>
       <c r="W329" t="inlineStr"/>
       <c r="X329" t="inlineStr"/>
-      <c r="Y329" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z329" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA329" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB329" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC329" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AD329" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AE329" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF329" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AG329" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AH329" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AI329" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ329" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Y329" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA329" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC329" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD329" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF329" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG329" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH329" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI329" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ329" t="n">
+        <v>4</v>
       </c>
       <c r="AK329" t="inlineStr"/>
       <c r="AL329" t="inlineStr"/>
       <c r="AM329" t="inlineStr"/>
       <c r="AN329" t="inlineStr"/>
-      <c r="AO329" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="AP329" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="AQ329" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AR329" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="AO329" t="n">
+        <v>135</v>
+      </c>
+      <c r="AP329" t="n">
+        <v>89</v>
+      </c>
+      <c r="AQ329" t="n">
+        <v>45</v>
+      </c>
+      <c r="AR329" t="n">
+        <v>27</v>
       </c>
       <c r="AS329" t="inlineStr"/>
       <c r="AT329" t="inlineStr"/>
@@ -68147,15 +67231,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC329" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BD329" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="BC329" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD329" t="n">
+        <v>3</v>
       </c>
       <c r="BE329" t="inlineStr"/>
       <c r="BF329" t="inlineStr"/>
@@ -68199,15 +67279,11 @@
           <t>20 009</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G330" t="n">
+        <v>0</v>
+      </c>
+      <c r="H330" t="n">
+        <v>0</v>
       </c>
       <c r="I330" t="inlineStr">
         <is>
@@ -68241,121 +67317,77 @@
           <t>29%</t>
         </is>
       </c>
-      <c r="Q330" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R330" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S330" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T330" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U330" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V330" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Q330" t="n">
+        <v>14</v>
+      </c>
+      <c r="R330" t="n">
+        <v>15</v>
+      </c>
+      <c r="S330" t="n">
+        <v>4</v>
+      </c>
+      <c r="T330" t="n">
+        <v>5</v>
+      </c>
+      <c r="U330" t="n">
+        <v>7</v>
+      </c>
+      <c r="V330" t="n">
+        <v>6</v>
       </c>
       <c r="W330" t="inlineStr"/>
       <c r="X330" t="inlineStr"/>
-      <c r="Y330" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z330" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA330" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB330" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC330" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AD330" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AE330" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AF330" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG330" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH330" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AI330" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ330" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y330" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA330" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB330" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC330" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD330" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE330" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF330" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG330" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH330" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI330" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ330" t="n">
+        <v>2</v>
       </c>
       <c r="AK330" t="inlineStr"/>
       <c r="AL330" t="inlineStr"/>
       <c r="AM330" t="inlineStr"/>
       <c r="AN330" t="inlineStr"/>
-      <c r="AO330" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AP330" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="AQ330" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="AR330" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="AO330" t="n">
+        <v>112</v>
+      </c>
+      <c r="AP330" t="n">
+        <v>91</v>
+      </c>
+      <c r="AQ330" t="n">
+        <v>76</v>
+      </c>
+      <c r="AR330" t="n">
+        <v>54</v>
       </c>
       <c r="AS330" t="inlineStr"/>
       <c r="AT330" t="inlineStr"/>
@@ -68393,15 +67425,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC330" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BD330" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="BC330" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD330" t="n">
+        <v>4</v>
       </c>
       <c r="BE330" t="inlineStr"/>
       <c r="BF330" t="inlineStr"/>
@@ -68445,15 +67473,11 @@
           <t>15 285</t>
         </is>
       </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G331" t="n">
+        <v>1</v>
+      </c>
+      <c r="H331" t="n">
+        <v>1</v>
       </c>
       <c r="I331" t="inlineStr">
         <is>
@@ -68487,121 +67511,77 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="Q331" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R331" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S331" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T331" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U331" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V331" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q331" t="n">
+        <v>31</v>
+      </c>
+      <c r="R331" t="n">
+        <v>6</v>
+      </c>
+      <c r="S331" t="n">
+        <v>10</v>
+      </c>
+      <c r="T331" t="n">
+        <v>1</v>
+      </c>
+      <c r="U331" t="n">
+        <v>10</v>
+      </c>
+      <c r="V331" t="n">
+        <v>2</v>
       </c>
       <c r="W331" t="inlineStr"/>
       <c r="X331" t="inlineStr"/>
-      <c r="Y331" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z331" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA331" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB331" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC331" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AD331" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AE331" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF331" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AG331" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH331" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AI331" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ331" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y331" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z331" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA331" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB331" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC331" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD331" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE331" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF331" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG331" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH331" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI331" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ331" t="n">
+        <v>5</v>
       </c>
       <c r="AK331" t="inlineStr"/>
       <c r="AL331" t="inlineStr"/>
       <c r="AM331" t="inlineStr"/>
       <c r="AN331" t="inlineStr"/>
-      <c r="AO331" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="AP331" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AQ331" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AR331" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="AO331" t="n">
+        <v>102</v>
+      </c>
+      <c r="AP331" t="n">
+        <v>90</v>
+      </c>
+      <c r="AQ331" t="n">
+        <v>86</v>
+      </c>
+      <c r="AR331" t="n">
+        <v>32</v>
       </c>
       <c r="AS331" t="inlineStr"/>
       <c r="AT331" t="inlineStr"/>
@@ -68639,25 +67619,17 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC331" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BD331" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BE331" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF331" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="BC331" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD331" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE331" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF331" t="n">
+        <v>2</v>
       </c>
       <c r="BG331" t="inlineStr"/>
       <c r="BH331" t="inlineStr"/>
@@ -68699,15 +67671,11 @@
           <t>28 800</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G332" t="n">
+        <v>0</v>
+      </c>
+      <c r="H332" t="n">
+        <v>2</v>
       </c>
       <c r="I332" t="inlineStr">
         <is>
@@ -68741,121 +67709,77 @@
           <t>70%</t>
         </is>
       </c>
-      <c r="Q332" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R332" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S332" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T332" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U332" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V332" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q332" t="n">
+        <v>8</v>
+      </c>
+      <c r="R332" t="n">
+        <v>13</v>
+      </c>
+      <c r="S332" t="n">
+        <v>2</v>
+      </c>
+      <c r="T332" t="n">
+        <v>5</v>
+      </c>
+      <c r="U332" t="n">
+        <v>4</v>
+      </c>
+      <c r="V332" t="n">
+        <v>4</v>
       </c>
       <c r="W332" t="inlineStr"/>
       <c r="X332" t="inlineStr"/>
-      <c r="Y332" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z332" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA332" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB332" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC332" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AD332" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AE332" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF332" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG332" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AH332" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI332" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ332" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y332" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z332" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA332" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB332" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC332" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD332" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE332" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF332" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG332" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH332" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI332" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ332" t="n">
+        <v>3</v>
       </c>
       <c r="AK332" t="inlineStr"/>
       <c r="AL332" t="inlineStr"/>
       <c r="AM332" t="inlineStr"/>
       <c r="AN332" t="inlineStr"/>
-      <c r="AO332" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AP332" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="AQ332" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="AR332" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="AO332" t="n">
+        <v>96</v>
+      </c>
+      <c r="AP332" t="n">
+        <v>133</v>
+      </c>
+      <c r="AQ332" t="n">
+        <v>61</v>
+      </c>
+      <c r="AR332" t="n">
+        <v>47</v>
       </c>
       <c r="AS332" t="inlineStr"/>
       <c r="AT332" t="inlineStr"/>
@@ -68893,15 +67817,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC332" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BD332" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="BC332" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD332" t="n">
+        <v>4</v>
       </c>
       <c r="BE332" t="inlineStr"/>
       <c r="BF332" t="inlineStr"/>
@@ -68912,6 +67832,1106 @@
       <c r="BK332" t="inlineStr"/>
       <c r="BL332" t="inlineStr"/>
     </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>GdWtpsjm</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Attwell S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Anfield
+ (Liverpool)</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>61 276</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W333" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB333" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC333" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD333" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AE333" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF333" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG333" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH333" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI333" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ333" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK333" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="AL333" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="AM333" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AN333" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO333" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="AP333" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AQ333" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AR333" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AS333" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AT333" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AU333" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="AV333" t="inlineStr">
+        <is>
+          <t>slot arne</t>
+        </is>
+      </c>
+      <c r="AW333" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="AX333" t="inlineStr">
+        <is>
+          <t>frank thomas</t>
+        </is>
+      </c>
+      <c r="AY333" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ333" t="n">
+        <v>481</v>
+      </c>
+      <c r="BA333" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB333" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC333" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BD333" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BE333" t="inlineStr"/>
+      <c r="BF333" t="inlineStr"/>
+      <c r="BG333" t="inlineStr"/>
+      <c r="BH333" t="inlineStr"/>
+      <c r="BI333" t="inlineStr"/>
+      <c r="BJ333" t="inlineStr"/>
+      <c r="BK333" t="inlineStr"/>
+      <c r="BL333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>6RCbX36s</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>25.08.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Coote D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Vitality Stadium
+ (Bournemouth)</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>11 307</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>11 161</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W334" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z334" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB334" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC334" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD334" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE334" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF334" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG334" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AH334" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI334" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ334" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK334" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="AL334" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="AM334" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AN334" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AO334" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AP334" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AQ334" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AR334" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AS334" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AT334" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AU334" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="AV334" t="inlineStr">
+        <is>
+          <t>iraola andoni</t>
+        </is>
+      </c>
+      <c r="AW334" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="AX334" t="inlineStr">
+        <is>
+          <t>howe eddie</t>
+        </is>
+      </c>
+      <c r="AY334" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ334" t="n">
+        <v>481</v>
+      </c>
+      <c r="BA334" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB334" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC334" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BD334" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BE334" t="inlineStr"/>
+      <c r="BF334" t="inlineStr"/>
+      <c r="BG334" t="inlineStr"/>
+      <c r="BH334" t="inlineStr"/>
+      <c r="BI334" t="inlineStr"/>
+      <c r="BJ334" t="inlineStr"/>
+      <c r="BK334" t="inlineStr"/>
+      <c r="BL334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>61T7bt5t</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>25.08.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>England D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Molineux Stadium
+ (Wolverhampton)</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>31 750</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>31 235</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>Wolves</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB335" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC335" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AD335" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE335" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF335" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG335" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH335" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI335" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ335" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK335" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="AL335" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AM335" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AN335" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AO335" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="AP335" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AQ335" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AR335" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AS335" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AT335" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AU335" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="AV335" t="inlineStr">
+        <is>
+          <t>o neil gary</t>
+        </is>
+      </c>
+      <c r="AW335" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="AX335" t="inlineStr">
+        <is>
+          <t>maresca enzo</t>
+        </is>
+      </c>
+      <c r="AY335" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ335" t="n">
+        <v>481</v>
+      </c>
+      <c r="BA335" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB335" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC335" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD335" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BE335" t="inlineStr"/>
+      <c r="BF335" t="inlineStr"/>
+      <c r="BG335" t="inlineStr"/>
+      <c r="BH335" t="inlineStr"/>
+      <c r="BI335" t="inlineStr"/>
+      <c r="BJ335" t="inlineStr"/>
+      <c r="BK335" t="inlineStr"/>
+      <c r="BL335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>pKIPNiIj</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>25.08.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Langford O.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Swansea.com Stadium
+ (Swansea)</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>21 088</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>20 174</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>Swansea</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr"/>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W336" t="inlineStr"/>
+      <c r="X336" t="inlineStr"/>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z336" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB336" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC336" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AD336" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AE336" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF336" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG336" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH336" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI336" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ336" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK336" t="inlineStr"/>
+      <c r="AL336" t="inlineStr"/>
+      <c r="AM336" t="inlineStr"/>
+      <c r="AN336" t="inlineStr"/>
+      <c r="AO336" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AP336" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AQ336" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AR336" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AS336" t="inlineStr"/>
+      <c r="AT336" t="inlineStr"/>
+      <c r="AU336" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
+      <c r="AV336" t="inlineStr">
+        <is>
+          <t>williams luke</t>
+        </is>
+      </c>
+      <c r="AW336" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
+        </is>
+      </c>
+      <c r="AX336" t="inlineStr">
+        <is>
+          <t>bulut erol</t>
+        </is>
+      </c>
+      <c r="AY336" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ336" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA336" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB336" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC336" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD336" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE336" t="inlineStr"/>
+      <c r="BF336" t="inlineStr"/>
+      <c r="BG336" t="inlineStr"/>
+      <c r="BH336" t="inlineStr"/>
+      <c r="BI336" t="inlineStr"/>
+      <c r="BJ336" t="inlineStr"/>
+      <c r="BK336" t="inlineStr"/>
+      <c r="BL336" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL336"/>
+  <dimension ref="A1:BL363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67861,15 +67861,11 @@
         </is>
       </c>
       <c r="F333" t="inlineStr"/>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G333" t="n">
+        <v>2</v>
+      </c>
+      <c r="H333" t="n">
+        <v>0</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -67891,15 +67887,11 @@
           <t>Brentford</t>
         </is>
       </c>
-      <c r="M333" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="N333" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+      <c r="M333" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="N333" t="n">
+        <v>0.55</v>
       </c>
       <c r="O333" t="inlineStr">
         <is>
@@ -67911,155 +67903,95 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q333" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R333" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S333" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T333" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U333" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V333" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W333" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X333" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y333" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z333" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA333" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB333" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC333" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AD333" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AE333" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF333" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG333" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH333" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI333" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ333" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK333" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="AL333" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
-      <c r="AM333" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AN333" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AO333" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="AP333" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="AQ333" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="AR333" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="AS333" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AT333" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="Q333" t="n">
+        <v>19</v>
+      </c>
+      <c r="R333" t="n">
+        <v>9</v>
+      </c>
+      <c r="S333" t="n">
+        <v>8</v>
+      </c>
+      <c r="T333" t="n">
+        <v>2</v>
+      </c>
+      <c r="U333" t="n">
+        <v>4</v>
+      </c>
+      <c r="V333" t="n">
+        <v>4</v>
+      </c>
+      <c r="W333" t="n">
+        <v>7</v>
+      </c>
+      <c r="X333" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y333" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z333" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA333" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB333" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC333" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD333" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE333" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF333" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG333" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH333" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI333" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ333" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK333" t="n">
+        <v>650</v>
+      </c>
+      <c r="AL333" t="n">
+        <v>393</v>
+      </c>
+      <c r="AM333" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN333" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO333" t="n">
+        <v>142</v>
+      </c>
+      <c r="AP333" t="n">
+        <v>75</v>
+      </c>
+      <c r="AQ333" t="n">
+        <v>75</v>
+      </c>
+      <c r="AR333" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS333" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT333" t="n">
+        <v>18</v>
       </c>
       <c r="AU333" t="inlineStr">
         <is>
@@ -68095,15 +68027,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC333" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BD333" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="BC333" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD333" t="n">
+        <v>3</v>
       </c>
       <c r="BE333" t="inlineStr"/>
       <c r="BF333" t="inlineStr"/>
@@ -68147,15 +68075,11 @@
           <t>11 161</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G334" t="n">
+        <v>1</v>
+      </c>
+      <c r="H334" t="n">
+        <v>1</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -68177,15 +68101,11 @@
           <t>Newcastle</t>
         </is>
       </c>
-      <c r="M334" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="N334" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
+      <c r="M334" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="N334" t="n">
+        <v>1.96</v>
       </c>
       <c r="O334" t="inlineStr">
         <is>
@@ -68197,155 +68117,95 @@
           <t>61%</t>
         </is>
       </c>
-      <c r="Q334" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R334" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S334" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T334" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U334" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V334" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W334" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X334" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Y334" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z334" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA334" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB334" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC334" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AD334" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AE334" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF334" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG334" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AH334" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI334" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ334" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK334" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="AL334" t="inlineStr">
-        <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="AM334" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AN334" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AO334" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AP334" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="AQ334" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="AR334" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AS334" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AT334" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="Q334" t="n">
+        <v>16</v>
+      </c>
+      <c r="R334" t="n">
+        <v>14</v>
+      </c>
+      <c r="S334" t="n">
+        <v>4</v>
+      </c>
+      <c r="T334" t="n">
+        <v>5</v>
+      </c>
+      <c r="U334" t="n">
+        <v>8</v>
+      </c>
+      <c r="V334" t="n">
+        <v>6</v>
+      </c>
+      <c r="W334" t="n">
+        <v>7</v>
+      </c>
+      <c r="X334" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y334" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z334" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC334" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD334" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE334" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF334" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG334" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH334" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI334" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ334" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK334" t="n">
+        <v>318</v>
+      </c>
+      <c r="AL334" t="n">
+        <v>490</v>
+      </c>
+      <c r="AM334" t="n">
+        <v>22</v>
+      </c>
+      <c r="AN334" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO334" t="n">
+        <v>114</v>
+      </c>
+      <c r="AP334" t="n">
+        <v>108</v>
+      </c>
+      <c r="AQ334" t="n">
+        <v>46</v>
+      </c>
+      <c r="AR334" t="n">
+        <v>70</v>
+      </c>
+      <c r="AS334" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT334" t="n">
+        <v>14</v>
       </c>
       <c r="AU334" t="inlineStr">
         <is>
@@ -68381,15 +68241,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC334" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BD334" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="BC334" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD334" t="n">
+        <v>3</v>
       </c>
       <c r="BE334" t="inlineStr"/>
       <c r="BF334" t="inlineStr"/>
@@ -68433,15 +68289,11 @@
           <t>31 235</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="G335" t="n">
+        <v>2</v>
+      </c>
+      <c r="H335" t="n">
+        <v>6</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -68463,15 +68315,11 @@
           <t>Chelsea</t>
         </is>
       </c>
-      <c r="M335" t="inlineStr">
-        <is>
-          <t>2.16</t>
-        </is>
-      </c>
-      <c r="N335" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="M335" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="N335" t="n">
+        <v>2.65</v>
       </c>
       <c r="O335" t="inlineStr">
         <is>
@@ -68483,155 +68331,95 @@
           <t>62%</t>
         </is>
       </c>
-      <c r="Q335" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R335" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S335" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T335" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U335" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V335" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W335" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="X335" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Y335" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z335" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA335" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB335" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC335" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AD335" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AE335" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF335" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG335" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AH335" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AI335" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ335" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK335" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="AL335" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="AM335" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AN335" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AO335" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AP335" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AQ335" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="AR335" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="AS335" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AT335" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="Q335" t="n">
+        <v>12</v>
+      </c>
+      <c r="R335" t="n">
+        <v>14</v>
+      </c>
+      <c r="S335" t="n">
+        <v>4</v>
+      </c>
+      <c r="T335" t="n">
+        <v>8</v>
+      </c>
+      <c r="U335" t="n">
+        <v>8</v>
+      </c>
+      <c r="V335" t="n">
+        <v>3</v>
+      </c>
+      <c r="W335" t="n">
+        <v>14</v>
+      </c>
+      <c r="X335" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y335" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z335" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA335" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB335" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC335" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD335" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE335" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF335" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG335" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH335" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI335" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ335" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK335" t="n">
+        <v>301</v>
+      </c>
+      <c r="AL335" t="n">
+        <v>487</v>
+      </c>
+      <c r="AM335" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN335" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO335" t="n">
+        <v>77</v>
+      </c>
+      <c r="AP335" t="n">
+        <v>120</v>
+      </c>
+      <c r="AQ335" t="n">
+        <v>48</v>
+      </c>
+      <c r="AR335" t="n">
+        <v>56</v>
+      </c>
+      <c r="AS335" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT335" t="n">
+        <v>18</v>
       </c>
       <c r="AU335" t="inlineStr">
         <is>
@@ -68667,15 +68455,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC335" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD335" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="BC335" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD335" t="n">
+        <v>3</v>
       </c>
       <c r="BE335" t="inlineStr"/>
       <c r="BF335" t="inlineStr"/>
@@ -68719,15 +68503,11 @@
           <t>20 174</t>
         </is>
       </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G336" t="n">
+        <v>1</v>
+      </c>
+      <c r="H336" t="n">
+        <v>1</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -68761,121 +68541,77 @@
           <t>42%</t>
         </is>
       </c>
-      <c r="Q336" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R336" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S336" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T336" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U336" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V336" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q336" t="n">
+        <v>9</v>
+      </c>
+      <c r="R336" t="n">
+        <v>7</v>
+      </c>
+      <c r="S336" t="n">
+        <v>4</v>
+      </c>
+      <c r="T336" t="n">
+        <v>3</v>
+      </c>
+      <c r="U336" t="n">
+        <v>4</v>
+      </c>
+      <c r="V336" t="n">
+        <v>3</v>
       </c>
       <c r="W336" t="inlineStr"/>
       <c r="X336" t="inlineStr"/>
-      <c r="Y336" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z336" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA336" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB336" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC336" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AD336" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AE336" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF336" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG336" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AH336" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AI336" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ336" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Y336" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z336" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA336" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB336" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC336" t="n">
+        <v>31</v>
+      </c>
+      <c r="AD336" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE336" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF336" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG336" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH336" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI336" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ336" t="n">
+        <v>2</v>
       </c>
       <c r="AK336" t="inlineStr"/>
       <c r="AL336" t="inlineStr"/>
       <c r="AM336" t="inlineStr"/>
       <c r="AN336" t="inlineStr"/>
-      <c r="AO336" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AP336" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AQ336" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="AR336" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="AO336" t="n">
+        <v>111</v>
+      </c>
+      <c r="AP336" t="n">
+        <v>95</v>
+      </c>
+      <c r="AQ336" t="n">
+        <v>41</v>
+      </c>
+      <c r="AR336" t="n">
+        <v>38</v>
       </c>
       <c r="AS336" t="inlineStr"/>
       <c r="AT336" t="inlineStr"/>
@@ -68913,15 +68649,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC336" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD336" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC336" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD336" t="n">
+        <v>1</v>
       </c>
       <c r="BE336" t="inlineStr"/>
       <c r="BF336" t="inlineStr"/>
@@ -68932,6 +68664,6515 @@
       <c r="BK336" t="inlineStr"/>
       <c r="BL336" t="inlineStr"/>
     </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>vDEpovX1</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr"/>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>42DzSumJ</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>Hanworth</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>fBo5RVhP</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Walton &amp; Hersham</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr"/>
+      <c r="O337" t="inlineStr"/>
+      <c r="P337" t="inlineStr"/>
+      <c r="Q337" t="inlineStr"/>
+      <c r="R337" t="inlineStr"/>
+      <c r="S337" t="inlineStr"/>
+      <c r="T337" t="inlineStr"/>
+      <c r="U337" t="inlineStr"/>
+      <c r="V337" t="inlineStr"/>
+      <c r="W337" t="inlineStr"/>
+      <c r="X337" t="inlineStr"/>
+      <c r="Y337" t="inlineStr"/>
+      <c r="Z337" t="inlineStr"/>
+      <c r="AA337" t="inlineStr"/>
+      <c r="AB337" t="inlineStr"/>
+      <c r="AC337" t="inlineStr"/>
+      <c r="AD337" t="inlineStr"/>
+      <c r="AE337" t="inlineStr"/>
+      <c r="AF337" t="inlineStr"/>
+      <c r="AG337" t="inlineStr"/>
+      <c r="AH337" t="inlineStr"/>
+      <c r="AI337" t="inlineStr"/>
+      <c r="AJ337" t="inlineStr"/>
+      <c r="AK337" t="inlineStr"/>
+      <c r="AL337" t="inlineStr"/>
+      <c r="AM337" t="inlineStr"/>
+      <c r="AN337" t="inlineStr"/>
+      <c r="AO337" t="inlineStr"/>
+      <c r="AP337" t="inlineStr"/>
+      <c r="AQ337" t="inlineStr"/>
+      <c r="AR337" t="inlineStr"/>
+      <c r="AS337" t="inlineStr"/>
+      <c r="AT337" t="inlineStr"/>
+      <c r="AU337" t="inlineStr"/>
+      <c r="AV337" t="inlineStr"/>
+      <c r="AW337" t="inlineStr"/>
+      <c r="AX337" t="inlineStr"/>
+      <c r="AY337" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ337" t="n">
+        <v>483</v>
+      </c>
+      <c r="BA337" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB337" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC337" t="inlineStr"/>
+      <c r="BD337" t="inlineStr"/>
+      <c r="BE337" t="inlineStr"/>
+      <c r="BF337" t="inlineStr"/>
+      <c r="BG337" t="inlineStr"/>
+      <c r="BH337" t="inlineStr"/>
+      <c r="BI337" t="inlineStr"/>
+      <c r="BJ337" t="inlineStr"/>
+      <c r="BK337" t="inlineStr"/>
+      <c r="BL337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>hxlYyYo4</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>28.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Allison S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>City Ground
+ (Nottingham)</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>30 404</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>23 083</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Newcastle
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr"/>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W338" t="inlineStr"/>
+      <c r="X338" t="inlineStr"/>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z338" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB338" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC338" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AD338" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE338" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF338" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG338" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH338" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI338" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ338" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK338" t="inlineStr"/>
+      <c r="AL338" t="inlineStr"/>
+      <c r="AM338" t="inlineStr"/>
+      <c r="AN338" t="inlineStr"/>
+      <c r="AO338" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AP338" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AQ338" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AR338" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AS338" t="inlineStr"/>
+      <c r="AT338" t="inlineStr"/>
+      <c r="AU338" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="AV338" t="inlineStr">
+        <is>
+          <t>espirito santo</t>
+        </is>
+      </c>
+      <c r="AW338" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="AX338" t="inlineStr">
+        <is>
+          <t>howe eddie</t>
+        </is>
+      </c>
+      <c r="AY338" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ338" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA338" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB338" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC338" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BD338" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BE338" t="inlineStr"/>
+      <c r="BF338" t="inlineStr"/>
+      <c r="BG338" t="inlineStr"/>
+      <c r="BH338" t="inlineStr"/>
+      <c r="BI338" t="inlineStr"/>
+      <c r="BJ338" t="inlineStr"/>
+      <c r="BK338" t="inlineStr"/>
+      <c r="BL338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>U32wGjPp</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>28.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Linington J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>The Cherry Red Records Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>9 215</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>7 934</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>4KREuF43</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Ipswich</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr"/>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W339" t="inlineStr"/>
+      <c r="X339" t="inlineStr"/>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB339" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC339" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD339" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AE339" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF339" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG339" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH339" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI339" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ339" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK339" t="inlineStr"/>
+      <c r="AL339" t="inlineStr"/>
+      <c r="AM339" t="inlineStr"/>
+      <c r="AN339" t="inlineStr"/>
+      <c r="AO339" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AP339" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="AQ339" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AR339" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="AS339" t="inlineStr"/>
+      <c r="AT339" t="inlineStr"/>
+      <c r="AU339" t="inlineStr">
+        <is>
+          <t>zHJOSLsG</t>
+        </is>
+      </c>
+      <c r="AV339" t="inlineStr">
+        <is>
+          <t>jackson johnnie</t>
+        </is>
+      </c>
+      <c r="AW339" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="AX339" t="inlineStr">
+        <is>
+          <t>mckenna kieran</t>
+        </is>
+      </c>
+      <c r="AY339" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ339" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA339" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB339" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC339" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD339" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BE339" t="inlineStr"/>
+      <c r="BF339" t="inlineStr"/>
+      <c r="BG339" t="inlineStr"/>
+      <c r="BH339" t="inlineStr"/>
+      <c r="BI339" t="inlineStr"/>
+      <c r="BJ339" t="inlineStr"/>
+      <c r="BK339" t="inlineStr"/>
+      <c r="BL339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>hGzqjO6E</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>28.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Nield T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Cardiff City Stadium
+ (Cardiff)</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>33 280</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>7 225</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Southampton
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr"/>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W340" t="inlineStr"/>
+      <c r="X340" t="inlineStr"/>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB340" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC340" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AD340" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE340" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF340" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG340" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH340" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI340" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ340" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK340" t="inlineStr"/>
+      <c r="AL340" t="inlineStr"/>
+      <c r="AM340" t="inlineStr"/>
+      <c r="AN340" t="inlineStr"/>
+      <c r="AO340" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AP340" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="AQ340" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AR340" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AS340" t="inlineStr"/>
+      <c r="AT340" t="inlineStr"/>
+      <c r="AU340" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
+        </is>
+      </c>
+      <c r="AV340" t="inlineStr">
+        <is>
+          <t>bulut erol</t>
+        </is>
+      </c>
+      <c r="AW340" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="AX340" t="inlineStr">
+        <is>
+          <t>martin russell</t>
+        </is>
+      </c>
+      <c r="AY340" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ340" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA340" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB340" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC340" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BD340" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BE340" t="inlineStr"/>
+      <c r="BF340" t="inlineStr"/>
+      <c r="BG340" t="inlineStr"/>
+      <c r="BH340" t="inlineStr"/>
+      <c r="BI340" t="inlineStr"/>
+      <c r="BJ340" t="inlineStr"/>
+      <c r="BK340" t="inlineStr"/>
+      <c r="BL340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>OrHrRGXo</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>28.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Howard P.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Colchester Community Stadium
+ (Colchester)</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>10 105</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>6 716</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>xYu73rNn</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>Colchester</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Brentford
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr"/>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W341" t="inlineStr"/>
+      <c r="X341" t="inlineStr"/>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB341" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC341" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AD341" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE341" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF341" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG341" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH341" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI341" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ341" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK341" t="inlineStr"/>
+      <c r="AL341" t="inlineStr"/>
+      <c r="AM341" t="inlineStr"/>
+      <c r="AN341" t="inlineStr"/>
+      <c r="AO341" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AP341" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AQ341" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AR341" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AS341" t="inlineStr"/>
+      <c r="AT341" t="inlineStr"/>
+      <c r="AU341" t="inlineStr">
+        <is>
+          <t>MiVxbVgA</t>
+        </is>
+      </c>
+      <c r="AV341" t="inlineStr">
+        <is>
+          <t>cowley danny</t>
+        </is>
+      </c>
+      <c r="AW341" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="AX341" t="inlineStr">
+        <is>
+          <t>frank thomas</t>
+        </is>
+      </c>
+      <c r="AY341" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ341" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA341" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB341" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC341" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD341" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BE341" t="inlineStr"/>
+      <c r="BF341" t="inlineStr"/>
+      <c r="BG341" t="inlineStr"/>
+      <c r="BH341" t="inlineStr"/>
+      <c r="BI341" t="inlineStr"/>
+      <c r="BJ341" t="inlineStr"/>
+      <c r="BK341" t="inlineStr"/>
+      <c r="BL341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>WQF2UUMt</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>28.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Toner B.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Swansea.com Stadium
+ (Swansea)</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>21 088</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>6 000</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>Swansea</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>hl2V5JIl</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Wycombe
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr"/>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W342" t="inlineStr"/>
+      <c r="X342" t="inlineStr"/>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB342" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC342" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AD342" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AE342" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF342" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG342" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI342" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ342" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK342" t="inlineStr"/>
+      <c r="AL342" t="inlineStr"/>
+      <c r="AM342" t="inlineStr"/>
+      <c r="AN342" t="inlineStr"/>
+      <c r="AO342" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="AP342" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AQ342" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AR342" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AS342" t="inlineStr"/>
+      <c r="AT342" t="inlineStr"/>
+      <c r="AU342" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
+      <c r="AV342" t="inlineStr">
+        <is>
+          <t>williams luke</t>
+        </is>
+      </c>
+      <c r="AW342" t="inlineStr">
+        <is>
+          <t>65pf39vc</t>
+        </is>
+      </c>
+      <c r="AX342" t="inlineStr">
+        <is>
+          <t>bloomfield matt</t>
+        </is>
+      </c>
+      <c r="AY342" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ342" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA342" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB342" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC342" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BD342" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BE342" t="inlineStr"/>
+      <c r="BF342" t="inlineStr"/>
+      <c r="BG342" t="inlineStr"/>
+      <c r="BH342" t="inlineStr"/>
+      <c r="BI342" t="inlineStr"/>
+      <c r="BJ342" t="inlineStr"/>
+      <c r="BK342" t="inlineStr"/>
+      <c r="BL342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>rkazN4LU</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>28.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Bankes P.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>London Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>62 500</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>47 381</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+West Ham</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W343" t="inlineStr"/>
+      <c r="X343" t="inlineStr"/>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z343" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB343" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC343" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AD343" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE343" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF343" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG343" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH343" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI343" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ343" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK343" t="inlineStr"/>
+      <c r="AL343" t="inlineStr"/>
+      <c r="AM343" t="inlineStr"/>
+      <c r="AN343" t="inlineStr"/>
+      <c r="AO343" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AP343" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AQ343" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AR343" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AS343" t="inlineStr"/>
+      <c r="AT343" t="inlineStr"/>
+      <c r="AU343" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="AV343" t="inlineStr">
+        <is>
+          <t>lopetegui julen</t>
+        </is>
+      </c>
+      <c r="AW343" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="AX343" t="inlineStr">
+        <is>
+          <t>iraola andoni</t>
+        </is>
+      </c>
+      <c r="AY343" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ343" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA343" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB343" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC343" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BD343" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE343" t="inlineStr"/>
+      <c r="BF343" t="inlineStr"/>
+      <c r="BG343" t="inlineStr"/>
+      <c r="BH343" t="inlineStr"/>
+      <c r="BI343" t="inlineStr"/>
+      <c r="BJ343" t="inlineStr"/>
+      <c r="BK343" t="inlineStr"/>
+      <c r="BL343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>GEugARyP</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>28.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Smith J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Molineux Stadium
+ (Wolverhampton)</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>31 750</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>19 236</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Wolves</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr"/>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W344" t="inlineStr"/>
+      <c r="X344" t="inlineStr"/>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z344" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB344" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC344" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD344" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE344" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF344" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG344" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AH344" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI344" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ344" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK344" t="inlineStr"/>
+      <c r="AL344" t="inlineStr"/>
+      <c r="AM344" t="inlineStr"/>
+      <c r="AN344" t="inlineStr"/>
+      <c r="AO344" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AP344" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AQ344" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AR344" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AS344" t="inlineStr"/>
+      <c r="AT344" t="inlineStr"/>
+      <c r="AU344" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="AV344" t="inlineStr">
+        <is>
+          <t>o neil gary</t>
+        </is>
+      </c>
+      <c r="AW344" t="inlineStr">
+        <is>
+          <t>YuNX1zGT</t>
+        </is>
+      </c>
+      <c r="AX344" t="inlineStr">
+        <is>
+          <t>parker scott</t>
+        </is>
+      </c>
+      <c r="AY344" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ344" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA344" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB344" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC344" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BD344" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BE344" t="inlineStr"/>
+      <c r="BF344" t="inlineStr"/>
+      <c r="BG344" t="inlineStr"/>
+      <c r="BH344" t="inlineStr"/>
+      <c r="BI344" t="inlineStr"/>
+      <c r="BJ344" t="inlineStr"/>
+      <c r="BK344" t="inlineStr"/>
+      <c r="BL344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>Wn71woN8</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>27.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Stroud K.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>St. Andrew's Stadium
+ (Birmingham)</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>29 409</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>11 949</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>SWk4muv7</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Fulham
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr"/>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W345" t="inlineStr"/>
+      <c r="X345" t="inlineStr"/>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB345" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC345" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD345" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AE345" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF345" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG345" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AH345" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AI345" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ345" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK345" t="inlineStr"/>
+      <c r="AL345" t="inlineStr"/>
+      <c r="AM345" t="inlineStr"/>
+      <c r="AN345" t="inlineStr"/>
+      <c r="AO345" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AP345" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="AQ345" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AR345" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AS345" t="inlineStr"/>
+      <c r="AT345" t="inlineStr"/>
+      <c r="AU345" t="inlineStr">
+        <is>
+          <t>Uu6L6Igl</t>
+        </is>
+      </c>
+      <c r="AV345" t="inlineStr">
+        <is>
+          <t>davies chris</t>
+        </is>
+      </c>
+      <c r="AW345" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="AX345" t="inlineStr">
+        <is>
+          <t>silva marco</t>
+        </is>
+      </c>
+      <c r="AY345" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ345" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA345" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB345" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC345" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BD345" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BE345" t="inlineStr"/>
+      <c r="BF345" t="inlineStr"/>
+      <c r="BG345" t="inlineStr"/>
+      <c r="BH345" t="inlineStr"/>
+      <c r="BI345" t="inlineStr"/>
+      <c r="BJ345" t="inlineStr"/>
+      <c r="BK345" t="inlineStr"/>
+      <c r="BL345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>EkqxE9x0</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>27.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Donohue M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Selhurst Park
+ (London)</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>25 486</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>12 503</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Crystal Palace</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Norwich</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr"/>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W346" t="inlineStr"/>
+      <c r="X346" t="inlineStr"/>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB346" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC346" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AD346" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE346" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF346" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG346" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH346" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI346" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ346" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK346" t="inlineStr"/>
+      <c r="AL346" t="inlineStr"/>
+      <c r="AM346" t="inlineStr"/>
+      <c r="AN346" t="inlineStr"/>
+      <c r="AO346" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AP346" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AQ346" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AR346" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AS346" t="inlineStr"/>
+      <c r="AT346" t="inlineStr"/>
+      <c r="AU346" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="AV346" t="inlineStr">
+        <is>
+          <t>glasner oliver</t>
+        </is>
+      </c>
+      <c r="AW346" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="AX346" t="inlineStr">
+        <is>
+          <t>thorup johannes</t>
+        </is>
+      </c>
+      <c r="AY346" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ346" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA346" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB346" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC346" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BD346" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BE346" t="inlineStr"/>
+      <c r="BF346" t="inlineStr"/>
+      <c r="BG346" t="inlineStr"/>
+      <c r="BH346" t="inlineStr"/>
+      <c r="BI346" t="inlineStr"/>
+      <c r="BJ346" t="inlineStr"/>
+      <c r="BK346" t="inlineStr"/>
+      <c r="BL346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>dUjtW2Fr</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Reeves T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Oakwell
+ (Barnsley)</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>23 287</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>10 739</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>UNGEKMx6</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Barnsley</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Sheffield Utd</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr"/>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W347" t="inlineStr"/>
+      <c r="X347" t="inlineStr"/>
+      <c r="Y347" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z347" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB347" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC347" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AD347" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AE347" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF347" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG347" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AH347" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI347" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ347" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK347" t="inlineStr"/>
+      <c r="AL347" t="inlineStr"/>
+      <c r="AM347" t="inlineStr"/>
+      <c r="AN347" t="inlineStr"/>
+      <c r="AO347" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AP347" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AQ347" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AR347" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AS347" t="inlineStr"/>
+      <c r="AT347" t="inlineStr"/>
+      <c r="AU347" t="inlineStr">
+        <is>
+          <t>bNLzN2wB</t>
+        </is>
+      </c>
+      <c r="AV347" t="inlineStr">
+        <is>
+          <t>clarke darrell</t>
+        </is>
+      </c>
+      <c r="AW347" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="AX347" t="inlineStr">
+        <is>
+          <t>wilder chris</t>
+        </is>
+      </c>
+      <c r="AY347" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ347" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA347" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB347" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC347" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BD347" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BE347" t="inlineStr"/>
+      <c r="BF347" t="inlineStr"/>
+      <c r="BG347" t="inlineStr"/>
+      <c r="BH347" t="inlineStr"/>
+      <c r="BI347" t="inlineStr"/>
+      <c r="BJ347" t="inlineStr"/>
+      <c r="BK347" t="inlineStr"/>
+      <c r="BL347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>MFnpCm7C</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Stockbridge S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Holker Street
+ (Barrow in Furness)</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>6 500</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>3 003</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>KKJL7QXd</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Barrow</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Iug0YO0Q</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Derby</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr"/>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W348" t="inlineStr"/>
+      <c r="X348" t="inlineStr"/>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB348" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC348" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AD348" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AE348" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF348" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG348" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH348" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI348" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ348" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK348" t="inlineStr"/>
+      <c r="AL348" t="inlineStr"/>
+      <c r="AM348" t="inlineStr"/>
+      <c r="AN348" t="inlineStr"/>
+      <c r="AO348" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AP348" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AQ348" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AR348" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AS348" t="inlineStr"/>
+      <c r="AT348" t="inlineStr"/>
+      <c r="AU348" t="inlineStr">
+        <is>
+          <t>joDBK9gn</t>
+        </is>
+      </c>
+      <c r="AV348" t="inlineStr">
+        <is>
+          <t>clemence stephen</t>
+        </is>
+      </c>
+      <c r="AW348" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
+      <c r="AX348" t="inlineStr">
+        <is>
+          <t>warne paul</t>
+        </is>
+      </c>
+      <c r="AY348" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ348" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA348" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB348" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC348" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BD348" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BE348" t="inlineStr"/>
+      <c r="BF348" t="inlineStr"/>
+      <c r="BG348" t="inlineStr"/>
+      <c r="BH348" t="inlineStr"/>
+      <c r="BI348" t="inlineStr"/>
+      <c r="BJ348" t="inlineStr"/>
+      <c r="BK348" t="inlineStr"/>
+      <c r="BL348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>UsklUtpe</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Backhouse A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Ewood Park
+ (Blackburn)</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>31 367</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>9 418</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>Blackburn</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>8EFIJthC</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Blackpool
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr"/>
+      <c r="N349" t="inlineStr"/>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W349" t="inlineStr"/>
+      <c r="X349" t="inlineStr"/>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z349" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB349" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC349" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AD349" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE349" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF349" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG349" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AH349" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI349" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ349" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK349" t="inlineStr"/>
+      <c r="AL349" t="inlineStr"/>
+      <c r="AM349" t="inlineStr"/>
+      <c r="AN349" t="inlineStr"/>
+      <c r="AO349" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AP349" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AQ349" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AR349" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AS349" t="inlineStr"/>
+      <c r="AT349" t="inlineStr"/>
+      <c r="AU349" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+      <c r="AV349" t="inlineStr">
+        <is>
+          <t>eustace john</t>
+        </is>
+      </c>
+      <c r="AW349" t="inlineStr">
+        <is>
+          <t>2e9kg9n1</t>
+        </is>
+      </c>
+      <c r="AX349" t="inlineStr">
+        <is>
+          <t>keogh richard</t>
+        </is>
+      </c>
+      <c r="AY349" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ349" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA349" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB349" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC349" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BD349" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE349" t="inlineStr"/>
+      <c r="BF349" t="inlineStr"/>
+      <c r="BG349" t="inlineStr"/>
+      <c r="BH349" t="inlineStr"/>
+      <c r="BI349" t="inlineStr"/>
+      <c r="BJ349" t="inlineStr"/>
+      <c r="BK349" t="inlineStr"/>
+      <c r="BL349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>ddFjPf2b</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Chilowicz A.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Amex Stadium
+ (Brighton)</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>31 876</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>19 175</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Brighton</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>QVmLl54o</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Crawley</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr"/>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W350" t="inlineStr"/>
+      <c r="X350" t="inlineStr"/>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB350" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC350" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AD350" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AE350" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF350" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG350" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH350" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI350" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ350" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK350" t="inlineStr"/>
+      <c r="AL350" t="inlineStr"/>
+      <c r="AM350" t="inlineStr"/>
+      <c r="AN350" t="inlineStr"/>
+      <c r="AO350" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AP350" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AQ350" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AR350" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AS350" t="inlineStr"/>
+      <c r="AT350" t="inlineStr"/>
+      <c r="AU350" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="AV350" t="inlineStr">
+        <is>
+          <t>hurzeler fabian</t>
+        </is>
+      </c>
+      <c r="AW350" t="inlineStr">
+        <is>
+          <t>COqtASrJ</t>
+        </is>
+      </c>
+      <c r="AX350" t="inlineStr">
+        <is>
+          <t>lindsey scott</t>
+        </is>
+      </c>
+      <c r="AY350" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ350" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA350" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB350" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC350" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BD350" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BE350" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF350" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG350" t="inlineStr"/>
+      <c r="BH350" t="inlineStr"/>
+      <c r="BI350" t="inlineStr"/>
+      <c r="BJ350" t="inlineStr"/>
+      <c r="BK350" t="inlineStr"/>
+      <c r="BL350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>Sh9BS8ig</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Finnie W.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Coventry Building Society Arena
+ (Coventry)</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>32 753</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>11 808</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>GOvB22xg</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Coventry</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>vgOBT43c</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Oxford Utd</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr"/>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W351" t="inlineStr"/>
+      <c r="X351" t="inlineStr"/>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB351" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC351" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD351" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE351" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF351" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG351" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH351" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI351" t="inlineStr"/>
+      <c r="AJ351" t="inlineStr"/>
+      <c r="AK351" t="inlineStr"/>
+      <c r="AL351" t="inlineStr"/>
+      <c r="AM351" t="inlineStr"/>
+      <c r="AN351" t="inlineStr"/>
+      <c r="AO351" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AP351" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AQ351" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AR351" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AS351" t="inlineStr"/>
+      <c r="AT351" t="inlineStr"/>
+      <c r="AU351" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
+        </is>
+      </c>
+      <c r="AV351" t="inlineStr">
+        <is>
+          <t>robins mark</t>
+        </is>
+      </c>
+      <c r="AW351" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
+      <c r="AX351" t="inlineStr">
+        <is>
+          <t>buckingham des</t>
+        </is>
+      </c>
+      <c r="AY351" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ351" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA351" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB351" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC351" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BD351" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BE351" t="inlineStr"/>
+      <c r="BF351" t="inlineStr"/>
+      <c r="BG351" t="inlineStr"/>
+      <c r="BH351" t="inlineStr"/>
+      <c r="BI351" t="inlineStr"/>
+      <c r="BJ351" t="inlineStr"/>
+      <c r="BK351" t="inlineStr"/>
+      <c r="BL351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>dAfPwfHi</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Bell J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Goodison Park
+ (Liverpool)</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>39 572</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>37 245</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Everton</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>hlzYDy5q</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Doncaster</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr"/>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W352" t="inlineStr"/>
+      <c r="X352" t="inlineStr"/>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB352" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC352" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AD352" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AE352" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF352" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG352" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH352" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI352" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ352" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK352" t="inlineStr"/>
+      <c r="AL352" t="inlineStr"/>
+      <c r="AM352" t="inlineStr"/>
+      <c r="AN352" t="inlineStr"/>
+      <c r="AO352" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="AP352" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AQ352" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AR352" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AS352" t="inlineStr"/>
+      <c r="AT352" t="inlineStr"/>
+      <c r="AU352" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="AV352" t="inlineStr">
+        <is>
+          <t>dyche sean</t>
+        </is>
+      </c>
+      <c r="AW352" t="inlineStr">
+        <is>
+          <t>pSZhI8SM</t>
+        </is>
+      </c>
+      <c r="AX352" t="inlineStr">
+        <is>
+          <t>mccann grant</t>
+        </is>
+      </c>
+      <c r="AY352" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ352" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA352" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB352" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC352" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BD352" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BE352" t="inlineStr"/>
+      <c r="BF352" t="inlineStr"/>
+      <c r="BG352" t="inlineStr"/>
+      <c r="BH352" t="inlineStr"/>
+      <c r="BI352" t="inlineStr"/>
+      <c r="BJ352" t="inlineStr"/>
+      <c r="BK352" t="inlineStr"/>
+      <c r="BL352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>pWQ6LC1N</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Joyce R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Highbury Stadium
+ (Fleetwood)</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>5 327</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>1 744</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>tCZ3D68d</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Fleetwood</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>KMfM7P4b</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Rotherham</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr"/>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W353" t="inlineStr"/>
+      <c r="X353" t="inlineStr"/>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z353" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB353" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC353" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AD353" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AE353" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF353" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG353" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH353" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI353" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ353" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK353" t="inlineStr"/>
+      <c r="AL353" t="inlineStr"/>
+      <c r="AM353" t="inlineStr"/>
+      <c r="AN353" t="inlineStr"/>
+      <c r="AO353" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AP353" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="AQ353" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AR353" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AS353" t="inlineStr"/>
+      <c r="AT353" t="inlineStr"/>
+      <c r="AU353" t="inlineStr">
+        <is>
+          <t>d6KwHx8i</t>
+        </is>
+      </c>
+      <c r="AV353" t="inlineStr">
+        <is>
+          <t>adam charles</t>
+        </is>
+      </c>
+      <c r="AW353" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="AX353" t="inlineStr">
+        <is>
+          <t>evans steve</t>
+        </is>
+      </c>
+      <c r="AY353" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ353" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA353" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB353" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC353" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BD353" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BE353" t="inlineStr"/>
+      <c r="BF353" t="inlineStr"/>
+      <c r="BG353" t="inlineStr"/>
+      <c r="BH353" t="inlineStr"/>
+      <c r="BI353" t="inlineStr"/>
+      <c r="BJ353" t="inlineStr"/>
+      <c r="BK353" t="inlineStr"/>
+      <c r="BL353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>jiUEFsV1</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Corlett M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Blundell Park
+ (Cleethorpes)</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>9 052</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>6 364</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>OEaiS3za</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>Grimsby</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>llcCvIcG</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>Sheffield Wed
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W354" t="inlineStr"/>
+      <c r="X354" t="inlineStr"/>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z354" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB354" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC354" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD354" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AE354" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF354" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG354" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH354" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI354" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ354" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK354" t="inlineStr"/>
+      <c r="AL354" t="inlineStr"/>
+      <c r="AM354" t="inlineStr"/>
+      <c r="AN354" t="inlineStr"/>
+      <c r="AO354" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AP354" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AQ354" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AR354" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AS354" t="inlineStr"/>
+      <c r="AT354" t="inlineStr"/>
+      <c r="AU354" t="inlineStr">
+        <is>
+          <t>SGvTSGmc</t>
+        </is>
+      </c>
+      <c r="AV354" t="inlineStr">
+        <is>
+          <t>artell david</t>
+        </is>
+      </c>
+      <c r="AW354" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+      <c r="AX354" t="inlineStr">
+        <is>
+          <t>rohl danny</t>
+        </is>
+      </c>
+      <c r="AY354" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ354" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA354" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB354" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC354" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BD354" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BE354" t="inlineStr"/>
+      <c r="BF354" t="inlineStr"/>
+      <c r="BG354" t="inlineStr"/>
+      <c r="BH354" t="inlineStr"/>
+      <c r="BI354" t="inlineStr"/>
+      <c r="BJ354" t="inlineStr"/>
+      <c r="BK354" t="inlineStr"/>
+      <c r="BL354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>dY0SOQjI</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Speedie B.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>EnviroVent Stadium
+ (Harrogate)</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>2 570</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>CQv5qrFt</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>Harrogate</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>x8IDVcbi</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Preston
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W355" t="inlineStr"/>
+      <c r="X355" t="inlineStr"/>
+      <c r="Y355" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z355" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB355" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC355" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD355" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE355" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF355" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG355" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH355" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI355" t="inlineStr"/>
+      <c r="AJ355" t="inlineStr"/>
+      <c r="AK355" t="inlineStr"/>
+      <c r="AL355" t="inlineStr"/>
+      <c r="AM355" t="inlineStr"/>
+      <c r="AN355" t="inlineStr"/>
+      <c r="AO355" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AP355" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AQ355" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AR355" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AS355" t="inlineStr"/>
+      <c r="AT355" t="inlineStr"/>
+      <c r="AU355" t="inlineStr">
+        <is>
+          <t>ANwVL1Tp</t>
+        </is>
+      </c>
+      <c r="AV355" t="inlineStr">
+        <is>
+          <t>weaver simon</t>
+        </is>
+      </c>
+      <c r="AW355" t="inlineStr">
+        <is>
+          <t>lGE8iEO1</t>
+        </is>
+      </c>
+      <c r="AX355" t="inlineStr">
+        <is>
+          <t>heckingbottom paul</t>
+        </is>
+      </c>
+      <c r="AY355" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ355" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA355" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB355" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC355" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD355" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BE355" t="inlineStr"/>
+      <c r="BF355" t="inlineStr"/>
+      <c r="BG355" t="inlineStr"/>
+      <c r="BH355" t="inlineStr"/>
+      <c r="BI355" t="inlineStr"/>
+      <c r="BJ355" t="inlineStr"/>
+      <c r="BK355" t="inlineStr"/>
+      <c r="BL355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>hO8aNYWA</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Smith L.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>King Power Stadium
+ (Leicester)</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>32 261</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>13 011</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Leicester</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>jVhkb1QE</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Tranmere</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W356" t="inlineStr"/>
+      <c r="X356" t="inlineStr"/>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB356" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC356" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD356" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE356" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF356" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG356" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH356" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI356" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ356" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK356" t="inlineStr"/>
+      <c r="AL356" t="inlineStr"/>
+      <c r="AM356" t="inlineStr"/>
+      <c r="AN356" t="inlineStr"/>
+      <c r="AO356" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="AP356" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AQ356" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AR356" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AS356" t="inlineStr"/>
+      <c r="AT356" t="inlineStr"/>
+      <c r="AU356" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="AV356" t="inlineStr">
+        <is>
+          <t>cooper steven</t>
+        </is>
+      </c>
+      <c r="AW356" t="inlineStr">
+        <is>
+          <t>2L1wFbM5</t>
+        </is>
+      </c>
+      <c r="AX356" t="inlineStr">
+        <is>
+          <t>adkins nigel</t>
+        </is>
+      </c>
+      <c r="AY356" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ356" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA356" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB356" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC356" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BD356" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE356" t="inlineStr"/>
+      <c r="BF356" t="inlineStr"/>
+      <c r="BG356" t="inlineStr"/>
+      <c r="BH356" t="inlineStr"/>
+      <c r="BI356" t="inlineStr"/>
+      <c r="BJ356" t="inlineStr"/>
+      <c r="BK356" t="inlineStr"/>
+      <c r="BL356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>vDA9yPiL</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Rock D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>The Den
+ (London)</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>20 146</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>5 875</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>KKyYcus9</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Leyton Orient
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr"/>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W357" t="inlineStr"/>
+      <c r="X357" t="inlineStr"/>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z357" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB357" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC357" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AD357" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE357" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF357" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG357" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AH357" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AI357" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ357" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK357" t="inlineStr"/>
+      <c r="AL357" t="inlineStr"/>
+      <c r="AM357" t="inlineStr"/>
+      <c r="AN357" t="inlineStr"/>
+      <c r="AO357" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AP357" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AQ357" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AR357" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AS357" t="inlineStr"/>
+      <c r="AT357" t="inlineStr"/>
+      <c r="AU357" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+      <c r="AV357" t="inlineStr">
+        <is>
+          <t>harris neil</t>
+        </is>
+      </c>
+      <c r="AW357" t="inlineStr">
+        <is>
+          <t>C6Wq1Q6e</t>
+        </is>
+      </c>
+      <c r="AX357" t="inlineStr">
+        <is>
+          <t>wellens richie</t>
+        </is>
+      </c>
+      <c r="AY357" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ357" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA357" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB357" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC357" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD357" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BE357" t="inlineStr"/>
+      <c r="BF357" t="inlineStr"/>
+      <c r="BG357" t="inlineStr"/>
+      <c r="BH357" t="inlineStr"/>
+      <c r="BI357" t="inlineStr"/>
+      <c r="BJ357" t="inlineStr"/>
+      <c r="BK357" t="inlineStr"/>
+      <c r="BL357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>hzeTFV7m</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Doughty L.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Loftus Road
+ (London)</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>18 439</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>7 132</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+QPR</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Luton</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr"/>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W358" t="inlineStr"/>
+      <c r="X358" t="inlineStr"/>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB358" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC358" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AD358" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE358" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF358" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG358" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH358" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI358" t="inlineStr"/>
+      <c r="AJ358" t="inlineStr"/>
+      <c r="AK358" t="inlineStr"/>
+      <c r="AL358" t="inlineStr"/>
+      <c r="AM358" t="inlineStr"/>
+      <c r="AN358" t="inlineStr"/>
+      <c r="AO358" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AP358" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AQ358" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AR358" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AS358" t="inlineStr"/>
+      <c r="AT358" t="inlineStr"/>
+      <c r="AU358" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="AV358" t="inlineStr">
+        <is>
+          <t>cifuentes marti</t>
+        </is>
+      </c>
+      <c r="AW358" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="AX358" t="inlineStr">
+        <is>
+          <t>edwards rob</t>
+        </is>
+      </c>
+      <c r="AY358" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ358" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA358" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB358" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC358" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BD358" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BE358" t="inlineStr"/>
+      <c r="BF358" t="inlineStr"/>
+      <c r="BG358" t="inlineStr"/>
+      <c r="BH358" t="inlineStr"/>
+      <c r="BI358" t="inlineStr"/>
+      <c r="BJ358" t="inlineStr"/>
+      <c r="BK358" t="inlineStr"/>
+      <c r="BL358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>Q9rcSKE7</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Gill S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>The Croud Meadow
+ (Shrewsbury)</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>9 877</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>3 220</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>EqfQ6qK4</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>Shrewsbury</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Or1bBrWD</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Bolton
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr"/>
+      <c r="N359" t="inlineStr"/>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W359" t="inlineStr"/>
+      <c r="X359" t="inlineStr"/>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB359" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC359" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AD359" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AE359" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF359" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG359" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AH359" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI359" t="inlineStr"/>
+      <c r="AJ359" t="inlineStr"/>
+      <c r="AK359" t="inlineStr"/>
+      <c r="AL359" t="inlineStr"/>
+      <c r="AM359" t="inlineStr"/>
+      <c r="AN359" t="inlineStr"/>
+      <c r="AO359" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AP359" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="AQ359" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AR359" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AS359" t="inlineStr"/>
+      <c r="AT359" t="inlineStr"/>
+      <c r="AU359" t="inlineStr">
+        <is>
+          <t>EqN1jJFK</t>
+        </is>
+      </c>
+      <c r="AV359" t="inlineStr">
+        <is>
+          <t>hurst paul</t>
+        </is>
+      </c>
+      <c r="AW359" t="inlineStr">
+        <is>
+          <t>EosAlOi5</t>
+        </is>
+      </c>
+      <c r="AX359" t="inlineStr">
+        <is>
+          <t>evatt ian</t>
+        </is>
+      </c>
+      <c r="AY359" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ359" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA359" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB359" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC359" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BD359" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BE359" t="inlineStr"/>
+      <c r="BF359" t="inlineStr"/>
+      <c r="BG359" t="inlineStr"/>
+      <c r="BH359" t="inlineStr"/>
+      <c r="BI359" t="inlineStr"/>
+      <c r="BJ359" t="inlineStr"/>
+      <c r="BK359" t="inlineStr"/>
+      <c r="BL359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>zJCJQnM5</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Duckworth E.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Bescot Stadium
+ (Walsall)</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>11 300</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>3 378</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>YgrfcLuL</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Walsall</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>xxxpBZl2</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Huddersfield</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr"/>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W360" t="inlineStr"/>
+      <c r="X360" t="inlineStr"/>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB360" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC360" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AD360" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AE360" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF360" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG360" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH360" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI360" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ360" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK360" t="inlineStr"/>
+      <c r="AL360" t="inlineStr"/>
+      <c r="AM360" t="inlineStr"/>
+      <c r="AN360" t="inlineStr"/>
+      <c r="AO360" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AP360" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AQ360" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AR360" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AS360" t="inlineStr"/>
+      <c r="AT360" t="inlineStr"/>
+      <c r="AU360" t="inlineStr">
+        <is>
+          <t>YTxm48Ng</t>
+        </is>
+      </c>
+      <c r="AV360" t="inlineStr">
+        <is>
+          <t>sadler mathew john</t>
+        </is>
+      </c>
+      <c r="AW360" t="inlineStr">
+        <is>
+          <t>KGX2o9A5</t>
+        </is>
+      </c>
+      <c r="AX360" t="inlineStr">
+        <is>
+          <t>duff michael</t>
+        </is>
+      </c>
+      <c r="AY360" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ360" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA360" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB360" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC360" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BD360" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BE360" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF360" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG360" t="inlineStr"/>
+      <c r="BH360" t="inlineStr"/>
+      <c r="BI360" t="inlineStr"/>
+      <c r="BJ360" t="inlineStr"/>
+      <c r="BK360" t="inlineStr"/>
+      <c r="BL360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>QkntzCGG</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Davies A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Vicarage Road
+ (Watford)</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>22 200</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>8 319</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Watford</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>WpGM6ELj</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Plymouth</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr"/>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W361" t="inlineStr"/>
+      <c r="X361" t="inlineStr"/>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB361" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC361" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AD361" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE361" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF361" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG361" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AH361" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI361" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ361" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK361" t="inlineStr"/>
+      <c r="AL361" t="inlineStr"/>
+      <c r="AM361" t="inlineStr"/>
+      <c r="AN361" t="inlineStr"/>
+      <c r="AO361" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AP361" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AQ361" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="AR361" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AS361" t="inlineStr"/>
+      <c r="AT361" t="inlineStr"/>
+      <c r="AU361" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="AV361" t="inlineStr">
+        <is>
+          <t>cleverley tom</t>
+        </is>
+      </c>
+      <c r="AW361" t="inlineStr">
+        <is>
+          <t>WfXv1DCa</t>
+        </is>
+      </c>
+      <c r="AX361" t="inlineStr">
+        <is>
+          <t>rooney wayne</t>
+        </is>
+      </c>
+      <c r="AY361" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ361" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA361" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB361" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC361" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BD361" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE361" t="inlineStr"/>
+      <c r="BF361" t="inlineStr"/>
+      <c r="BG361" t="inlineStr"/>
+      <c r="BH361" t="inlineStr"/>
+      <c r="BI361" t="inlineStr"/>
+      <c r="BJ361" t="inlineStr"/>
+      <c r="BK361" t="inlineStr"/>
+      <c r="BL361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>rRQ6H30k</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:15</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Eltringham G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Riverside Stadium
+ (Middlesbrough)</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>34 742</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>17 408</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>6F0lvLNC</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>hSUajdSS</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Stoke
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W362" t="inlineStr"/>
+      <c r="X362" t="inlineStr"/>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB362" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC362" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD362" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AE362" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF362" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG362" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH362" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI362" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ362" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK362" t="inlineStr"/>
+      <c r="AL362" t="inlineStr"/>
+      <c r="AM362" t="inlineStr"/>
+      <c r="AN362" t="inlineStr"/>
+      <c r="AO362" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="AP362" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AQ362" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AR362" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AS362" t="inlineStr"/>
+      <c r="AT362" t="inlineStr"/>
+      <c r="AU362" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
+      <c r="AV362" t="inlineStr">
+        <is>
+          <t>carrick michael</t>
+        </is>
+      </c>
+      <c r="AW362" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="AX362" t="inlineStr">
+        <is>
+          <t>schumacher steven</t>
+        </is>
+      </c>
+      <c r="AY362" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ362" t="n">
+        <v>484</v>
+      </c>
+      <c r="BA362" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB362" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC362" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BD362" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BE362" t="inlineStr"/>
+      <c r="BF362" t="inlineStr"/>
+      <c r="BG362" t="inlineStr"/>
+      <c r="BH362" t="inlineStr"/>
+      <c r="BI362" t="inlineStr"/>
+      <c r="BJ362" t="inlineStr"/>
+      <c r="BK362" t="inlineStr"/>
+      <c r="BL362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>YqcO2yDl</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>30.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Madley R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Kenilworth Road
+ (Luton)</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>12 300</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>Luton</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>QPR</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr"/>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr"/>
+      <c r="X363" t="inlineStr"/>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC363" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AD363" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF363" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG363" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AH363" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI363" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK363" t="inlineStr"/>
+      <c r="AL363" t="inlineStr"/>
+      <c r="AM363" t="inlineStr"/>
+      <c r="AN363" t="inlineStr"/>
+      <c r="AO363" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AP363" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AQ363" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AR363" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AS363" t="inlineStr"/>
+      <c r="AT363" t="inlineStr"/>
+      <c r="AU363" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="AV363" t="inlineStr">
+        <is>
+          <t>edwards rob</t>
+        </is>
+      </c>
+      <c r="AW363" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="AX363" t="inlineStr">
+        <is>
+          <t>cifuentes marti</t>
+        </is>
+      </c>
+      <c r="AY363" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ363" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA363" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB363" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC363" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BD363" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BE363" t="inlineStr"/>
+      <c r="BF363" t="inlineStr"/>
+      <c r="BG363" t="inlineStr"/>
+      <c r="BH363" t="inlineStr"/>
+      <c r="BI363" t="inlineStr"/>
+      <c r="BJ363" t="inlineStr"/>
+      <c r="BK363" t="inlineStr"/>
+      <c r="BL363" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL490"/>
+  <dimension ref="A1:BL495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73854,15 +73854,11 @@
         </is>
       </c>
       <c r="F364" t="inlineStr"/>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G364" t="n">
+        <v>1</v>
+      </c>
+      <c r="H364" t="n">
+        <v>3</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
@@ -73884,15 +73880,11 @@
           <t>Manchester City</t>
         </is>
       </c>
-      <c r="M364" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="N364" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
+      <c r="M364" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="N364" t="n">
+        <v>1.84</v>
       </c>
       <c r="O364" t="inlineStr">
         <is>
@@ -73904,155 +73896,95 @@
           <t>71%</t>
         </is>
       </c>
-      <c r="Q364" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R364" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S364" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T364" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U364" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V364" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W364" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X364" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y364" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z364" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA364" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB364" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC364" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AD364" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AE364" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF364" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG364" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH364" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI364" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ364" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK364" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="AL364" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="AM364" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AN364" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AO364" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AP364" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="AQ364" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AR364" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AS364" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AT364" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="Q364" t="n">
+        <v>9</v>
+      </c>
+      <c r="R364" t="n">
+        <v>17</v>
+      </c>
+      <c r="S364" t="n">
+        <v>3</v>
+      </c>
+      <c r="T364" t="n">
+        <v>7</v>
+      </c>
+      <c r="U364" t="n">
+        <v>5</v>
+      </c>
+      <c r="V364" t="n">
+        <v>6</v>
+      </c>
+      <c r="W364" t="n">
+        <v>3</v>
+      </c>
+      <c r="X364" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y364" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z364" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA364" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB364" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC364" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD364" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE364" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF364" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG364" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH364" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI364" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ364" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK364" t="n">
+        <v>295</v>
+      </c>
+      <c r="AL364" t="n">
+        <v>530</v>
+      </c>
+      <c r="AM364" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN364" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO364" t="n">
+        <v>86</v>
+      </c>
+      <c r="AP364" t="n">
+        <v>148</v>
+      </c>
+      <c r="AQ364" t="n">
+        <v>40</v>
+      </c>
+      <c r="AR364" t="n">
+        <v>109</v>
+      </c>
+      <c r="AS364" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT364" t="n">
+        <v>15</v>
       </c>
       <c r="AU364" t="inlineStr">
         <is>
@@ -74088,15 +74020,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC364" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD364" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="BC364" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD364" t="n">
+        <v>4</v>
       </c>
       <c r="BE364" t="inlineStr"/>
       <c r="BF364" t="inlineStr"/>
@@ -74140,15 +74068,11 @@
           <t>16 955</t>
         </is>
       </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H365" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G365" t="n">
+        <v>3</v>
+      </c>
+      <c r="H365" t="n">
+        <v>1</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -74170,15 +74094,11 @@
           <t>Southampton</t>
         </is>
       </c>
-      <c r="M365" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="N365" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
+      <c r="M365" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="N365" t="n">
+        <v>1.74</v>
       </c>
       <c r="O365" t="inlineStr">
         <is>
@@ -74190,155 +74110,95 @@
           <t>63%</t>
         </is>
       </c>
-      <c r="Q365" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R365" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S365" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T365" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U365" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V365" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W365" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X365" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y365" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z365" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA365" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB365" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC365" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AD365" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AE365" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AF365" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG365" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH365" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI365" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ365" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK365" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="AL365" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="AM365" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AN365" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AO365" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AP365" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="AQ365" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="AR365" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="AS365" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AT365" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="Q365" t="n">
+        <v>20</v>
+      </c>
+      <c r="R365" t="n">
+        <v>18</v>
+      </c>
+      <c r="S365" t="n">
+        <v>7</v>
+      </c>
+      <c r="T365" t="n">
+        <v>6</v>
+      </c>
+      <c r="U365" t="n">
+        <v>8</v>
+      </c>
+      <c r="V365" t="n">
+        <v>7</v>
+      </c>
+      <c r="W365" t="n">
+        <v>7</v>
+      </c>
+      <c r="X365" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y365" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z365" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA365" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB365" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC365" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD365" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE365" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF365" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG365" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH365" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI365" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ365" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK365" t="n">
+        <v>351</v>
+      </c>
+      <c r="AL365" t="n">
+        <v>606</v>
+      </c>
+      <c r="AM365" t="n">
+        <v>17</v>
+      </c>
+      <c r="AN365" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO365" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP365" t="n">
+        <v>101</v>
+      </c>
+      <c r="AQ365" t="n">
+        <v>59</v>
+      </c>
+      <c r="AR365" t="n">
+        <v>61</v>
+      </c>
+      <c r="AS365" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT365" t="n">
+        <v>16</v>
       </c>
       <c r="AU365" t="inlineStr">
         <is>
@@ -74374,15 +74234,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC365" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BD365" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="BC365" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD365" t="n">
+        <v>5</v>
       </c>
       <c r="BE365" t="inlineStr"/>
       <c r="BF365" t="inlineStr"/>
@@ -74426,15 +74282,11 @@
           <t>38 805</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G366" t="n">
+        <v>2</v>
+      </c>
+      <c r="H366" t="n">
+        <v>3</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -74456,15 +74308,11 @@
           <t>Bournemouth</t>
         </is>
       </c>
-      <c r="M366" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="N366" t="inlineStr">
-        <is>
-          <t>2.44</t>
-        </is>
+      <c r="M366" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="N366" t="n">
+        <v>2.44</v>
       </c>
       <c r="O366" t="inlineStr">
         <is>
@@ -74476,155 +74324,95 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q366" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R366" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S366" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T366" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U366" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V366" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W366" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X366" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y366" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z366" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA366" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB366" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC366" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD366" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AE366" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF366" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG366" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH366" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AI366" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ366" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK366" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="AL366" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="AM366" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AN366" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AO366" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="AP366" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AQ366" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="AR366" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="AS366" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AT366" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="Q366" t="n">
+        <v>18</v>
+      </c>
+      <c r="R366" t="n">
+        <v>17</v>
+      </c>
+      <c r="S366" t="n">
+        <v>8</v>
+      </c>
+      <c r="T366" t="n">
+        <v>7</v>
+      </c>
+      <c r="U366" t="n">
+        <v>10</v>
+      </c>
+      <c r="V366" t="n">
+        <v>7</v>
+      </c>
+      <c r="W366" t="n">
+        <v>12</v>
+      </c>
+      <c r="X366" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y366" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z366" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA366" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB366" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC366" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD366" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE366" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF366" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG366" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH366" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI366" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ366" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK366" t="n">
+        <v>340</v>
+      </c>
+      <c r="AL366" t="n">
+        <v>376</v>
+      </c>
+      <c r="AM366" t="n">
+        <v>17</v>
+      </c>
+      <c r="AN366" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO366" t="n">
+        <v>121</v>
+      </c>
+      <c r="AP366" t="n">
+        <v>109</v>
+      </c>
+      <c r="AQ366" t="n">
+        <v>68</v>
+      </c>
+      <c r="AR366" t="n">
+        <v>61</v>
+      </c>
+      <c r="AS366" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT366" t="n">
+        <v>23</v>
       </c>
       <c r="AU366" t="inlineStr">
         <is>
@@ -74660,15 +74448,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC366" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD366" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="BC366" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD366" t="n">
+        <v>3</v>
       </c>
       <c r="BE366" t="inlineStr"/>
       <c r="BF366" t="inlineStr"/>
@@ -74712,15 +74496,11 @@
           <t>29 517</t>
         </is>
       </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H367" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G367" t="n">
+        <v>1</v>
+      </c>
+      <c r="H367" t="n">
+        <v>1</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -74742,15 +74522,11 @@
           <t>Fulham</t>
         </is>
       </c>
-      <c r="M367" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="N367" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
+      <c r="M367" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="N367" t="n">
+        <v>1.32</v>
       </c>
       <c r="O367" t="inlineStr">
         <is>
@@ -74762,155 +74538,95 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q367" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R367" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S367" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T367" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U367" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V367" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W367" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="X367" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Y367" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z367" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA367" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB367" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC367" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AD367" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AE367" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF367" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG367" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AH367" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI367" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ367" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK367" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="AL367" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AM367" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AN367" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AO367" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="AP367" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AQ367" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="AR367" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AS367" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AT367" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="Q367" t="n">
+        <v>11</v>
+      </c>
+      <c r="R367" t="n">
+        <v>9</v>
+      </c>
+      <c r="S367" t="n">
+        <v>4</v>
+      </c>
+      <c r="T367" t="n">
+        <v>4</v>
+      </c>
+      <c r="U367" t="n">
+        <v>4</v>
+      </c>
+      <c r="V367" t="n">
+        <v>2</v>
+      </c>
+      <c r="W367" t="n">
+        <v>16</v>
+      </c>
+      <c r="X367" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y367" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z367" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA367" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB367" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC367" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD367" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE367" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF367" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG367" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH367" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI367" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ367" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK367" t="n">
+        <v>395</v>
+      </c>
+      <c r="AL367" t="n">
+        <v>414</v>
+      </c>
+      <c r="AM367" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN367" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO367" t="n">
+        <v>88</v>
+      </c>
+      <c r="AP367" t="n">
+        <v>97</v>
+      </c>
+      <c r="AQ367" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR367" t="n">
+        <v>45</v>
+      </c>
+      <c r="AS367" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT367" t="n">
+        <v>12</v>
       </c>
       <c r="AU367" t="inlineStr">
         <is>
@@ -74946,15 +74662,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC367" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BD367" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="BC367" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD367" t="n">
+        <v>3</v>
       </c>
       <c r="BE367" t="inlineStr"/>
       <c r="BF367" t="inlineStr"/>
@@ -74998,15 +74710,11 @@
           <t>31 725</t>
         </is>
       </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H368" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G368" t="n">
+        <v>1</v>
+      </c>
+      <c r="H368" t="n">
+        <v>2</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -75028,15 +74736,11 @@
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="M368" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
-      <c r="N368" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
+      <c r="M368" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N368" t="n">
+        <v>0.82</v>
       </c>
       <c r="O368" t="inlineStr">
         <is>
@@ -75048,155 +74752,95 @@
           <t>43%</t>
         </is>
       </c>
-      <c r="Q368" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R368" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S368" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T368" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U368" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V368" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W368" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="X368" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Y368" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z368" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA368" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB368" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC368" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AD368" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AE368" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF368" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG368" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AH368" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AI368" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ368" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK368" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="AL368" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="AM368" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AN368" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AO368" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AP368" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="AQ368" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="AR368" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AS368" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AT368" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="Q368" t="n">
+        <v>9</v>
+      </c>
+      <c r="R368" t="n">
+        <v>10</v>
+      </c>
+      <c r="S368" t="n">
+        <v>3</v>
+      </c>
+      <c r="T368" t="n">
+        <v>5</v>
+      </c>
+      <c r="U368" t="n">
+        <v>4</v>
+      </c>
+      <c r="V368" t="n">
+        <v>4</v>
+      </c>
+      <c r="W368" t="n">
+        <v>28</v>
+      </c>
+      <c r="X368" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y368" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z368" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA368" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB368" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC368" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD368" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE368" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF368" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG368" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH368" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI368" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ368" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK368" t="n">
+        <v>496</v>
+      </c>
+      <c r="AL368" t="n">
+        <v>378</v>
+      </c>
+      <c r="AM368" t="n">
+        <v>22</v>
+      </c>
+      <c r="AN368" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO368" t="n">
+        <v>119</v>
+      </c>
+      <c r="AP368" t="n">
+        <v>87</v>
+      </c>
+      <c r="AQ368" t="n">
+        <v>46</v>
+      </c>
+      <c r="AR368" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS368" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT368" t="n">
+        <v>24</v>
       </c>
       <c r="AU368" t="inlineStr">
         <is>
@@ -75232,15 +74876,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC368" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BD368" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC368" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD368" t="n">
+        <v>1</v>
       </c>
       <c r="BE368" t="inlineStr"/>
       <c r="BF368" t="inlineStr"/>
@@ -75284,15 +74924,11 @@
           <t>29 918</t>
         </is>
       </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H369" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G369" t="n">
+        <v>1</v>
+      </c>
+      <c r="H369" t="n">
+        <v>1</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -75314,15 +74950,11 @@
           <t>Wolves</t>
         </is>
       </c>
-      <c r="M369" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="N369" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
+      <c r="M369" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="N369" t="n">
+        <v>1.36</v>
       </c>
       <c r="O369" t="inlineStr">
         <is>
@@ -75334,155 +74966,95 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q369" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R369" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S369" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T369" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U369" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V369" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W369" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X369" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Y369" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z369" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA369" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB369" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC369" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AD369" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AE369" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF369" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG369" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AH369" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AI369" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ369" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK369" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="AL369" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="AM369" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AN369" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AO369" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AP369" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="AQ369" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="AR369" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AS369" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AT369" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="Q369" t="n">
+        <v>16</v>
+      </c>
+      <c r="R369" t="n">
+        <v>11</v>
+      </c>
+      <c r="S369" t="n">
+        <v>5</v>
+      </c>
+      <c r="T369" t="n">
+        <v>3</v>
+      </c>
+      <c r="U369" t="n">
+        <v>7</v>
+      </c>
+      <c r="V369" t="n">
+        <v>4</v>
+      </c>
+      <c r="W369" t="n">
+        <v>5</v>
+      </c>
+      <c r="X369" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y369" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z369" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA369" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB369" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC369" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD369" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE369" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF369" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG369" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH369" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI369" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ369" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK369" t="n">
+        <v>359</v>
+      </c>
+      <c r="AL369" t="n">
+        <v>348</v>
+      </c>
+      <c r="AM369" t="n">
+        <v>17</v>
+      </c>
+      <c r="AN369" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO369" t="n">
+        <v>115</v>
+      </c>
+      <c r="AP369" t="n">
+        <v>89</v>
+      </c>
+      <c r="AQ369" t="n">
+        <v>66</v>
+      </c>
+      <c r="AR369" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS369" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT369" t="n">
+        <v>26</v>
       </c>
       <c r="AU369" t="inlineStr">
         <is>
@@ -75518,15 +75090,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC369" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BD369" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="BC369" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD369" t="n">
+        <v>4</v>
       </c>
       <c r="BE369" t="inlineStr"/>
       <c r="BF369" t="inlineStr"/>
@@ -75570,15 +75138,11 @@
           <t>60 326</t>
         </is>
       </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G370" t="n">
+        <v>1</v>
+      </c>
+      <c r="H370" t="n">
+        <v>1</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
@@ -75600,15 +75164,11 @@
           <t>Brighton</t>
         </is>
       </c>
-      <c r="M370" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="N370" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
+      <c r="M370" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N370" t="n">
+        <v>1.63</v>
       </c>
       <c r="O370" t="inlineStr">
         <is>
@@ -75620,155 +75180,95 @@
           <t>64%</t>
         </is>
       </c>
-      <c r="Q370" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R370" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S370" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T370" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U370" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V370" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W370" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X370" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y370" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z370" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA370" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB370" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC370" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AD370" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AE370" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF370" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG370" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH370" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI370" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AJ370" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK370" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="AL370" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="AM370" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AN370" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AO370" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="AP370" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AQ370" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="AR370" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="AS370" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AT370" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="Q370" t="n">
+        <v>11</v>
+      </c>
+      <c r="R370" t="n">
+        <v>22</v>
+      </c>
+      <c r="S370" t="n">
+        <v>7</v>
+      </c>
+      <c r="T370" t="n">
+        <v>4</v>
+      </c>
+      <c r="U370" t="n">
+        <v>1</v>
+      </c>
+      <c r="V370" t="n">
+        <v>11</v>
+      </c>
+      <c r="W370" t="n">
+        <v>8</v>
+      </c>
+      <c r="X370" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y370" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z370" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA370" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB370" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC370" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD370" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE370" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF370" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG370" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH370" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI370" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ370" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK370" t="n">
+        <v>293</v>
+      </c>
+      <c r="AL370" t="n">
+        <v>487</v>
+      </c>
+      <c r="AM370" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN370" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO370" t="n">
+        <v>82</v>
+      </c>
+      <c r="AP370" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ370" t="n">
+        <v>46</v>
+      </c>
+      <c r="AR370" t="n">
+        <v>69</v>
+      </c>
+      <c r="AS370" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT370" t="n">
+        <v>12</v>
       </c>
       <c r="AU370" t="inlineStr">
         <is>
@@ -75804,25 +75304,17 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC370" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BD370" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BE370" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF370" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BC370" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD370" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE370" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF370" t="n">
+        <v>0</v>
       </c>
       <c r="BG370" t="inlineStr"/>
       <c r="BH370" t="inlineStr"/>
@@ -75846,15 +75338,11 @@
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr"/>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H371" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G371" t="n">
+        <v>3</v>
+      </c>
+      <c r="H371" t="n">
+        <v>2</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -75955,15 +75443,11 @@
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr"/>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H372" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G372" t="n">
+        <v>3</v>
+      </c>
+      <c r="H372" t="n">
+        <v>1</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
@@ -76064,15 +75548,11 @@
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr"/>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H373" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G373" t="n">
+        <v>0</v>
+      </c>
+      <c r="H373" t="n">
+        <v>2</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -76173,15 +75653,11 @@
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr"/>
-      <c r="G374" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H374" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G374" t="n">
+        <v>6</v>
+      </c>
+      <c r="H374" t="n">
+        <v>1</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -76282,15 +75758,11 @@
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr"/>
-      <c r="G375" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H375" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G375" t="n">
+        <v>3</v>
+      </c>
+      <c r="H375" t="n">
+        <v>3</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -76390,15 +75862,11 @@
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr"/>
-      <c r="G376" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H376" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G376" t="n">
+        <v>0</v>
+      </c>
+      <c r="H376" t="n">
+        <v>3</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -76499,15 +75967,11 @@
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr"/>
-      <c r="G377" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G377" t="n">
+        <v>1</v>
+      </c>
+      <c r="H377" t="n">
+        <v>3</v>
       </c>
       <c r="I377" t="inlineStr">
         <is>
@@ -76608,15 +76072,11 @@
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr"/>
-      <c r="G378" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H378" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G378" t="n">
+        <v>1</v>
+      </c>
+      <c r="H378" t="n">
+        <v>1</v>
       </c>
       <c r="I378" t="inlineStr">
         <is>
@@ -76716,15 +76176,11 @@
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr"/>
-      <c r="G379" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H379" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G379" t="n">
+        <v>2</v>
+      </c>
+      <c r="H379" t="n">
+        <v>0</v>
       </c>
       <c r="I379" t="inlineStr">
         <is>
@@ -76825,15 +76281,11 @@
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr"/>
-      <c r="G380" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H380" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G380" t="n">
+        <v>1</v>
+      </c>
+      <c r="H380" t="n">
+        <v>2</v>
       </c>
       <c r="I380" t="inlineStr">
         <is>
@@ -76934,15 +76386,11 @@
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr"/>
-      <c r="G381" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H381" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G381" t="n">
+        <v>0</v>
+      </c>
+      <c r="H381" t="n">
+        <v>1</v>
       </c>
       <c r="I381" t="inlineStr">
         <is>
@@ -77043,15 +76491,11 @@
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr"/>
-      <c r="G382" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H382" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G382" t="n">
+        <v>3</v>
+      </c>
+      <c r="H382" t="n">
+        <v>0</v>
       </c>
       <c r="I382" t="inlineStr">
         <is>
@@ -77152,15 +76596,11 @@
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr"/>
-      <c r="G383" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H383" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G383" t="n">
+        <v>6</v>
+      </c>
+      <c r="H383" t="n">
+        <v>1</v>
       </c>
       <c r="I383" t="inlineStr">
         <is>
@@ -77261,15 +76701,11 @@
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr"/>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H384" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G384" t="n">
+        <v>0</v>
+      </c>
+      <c r="H384" t="n">
+        <v>1</v>
       </c>
       <c r="I384" t="inlineStr">
         <is>
@@ -77370,15 +76806,11 @@
       <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr"/>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H385" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G385" t="n">
+        <v>1</v>
+      </c>
+      <c r="H385" t="n">
+        <v>3</v>
       </c>
       <c r="I385" t="inlineStr">
         <is>
@@ -77479,15 +76911,11 @@
       <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr"/>
-      <c r="G386" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H386" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G386" t="n">
+        <v>2</v>
+      </c>
+      <c r="H386" t="n">
+        <v>2</v>
       </c>
       <c r="I386" t="inlineStr">
         <is>
@@ -77587,15 +77015,11 @@
       <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr"/>
-      <c r="G387" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H387" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G387" t="n">
+        <v>0</v>
+      </c>
+      <c r="H387" t="n">
+        <v>1</v>
       </c>
       <c r="I387" t="inlineStr">
         <is>
@@ -77696,15 +77120,11 @@
       <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H388" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G388" t="n">
+        <v>1</v>
+      </c>
+      <c r="H388" t="n">
+        <v>2</v>
       </c>
       <c r="I388" t="inlineStr">
         <is>
@@ -77805,15 +77225,11 @@
       <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr"/>
-      <c r="G389" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H389" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="G389" t="n">
+        <v>1</v>
+      </c>
+      <c r="H389" t="n">
+        <v>5</v>
       </c>
       <c r="I389" t="inlineStr">
         <is>
@@ -77914,15 +77330,11 @@
       <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr"/>
-      <c r="G390" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H390" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G390" t="n">
+        <v>5</v>
+      </c>
+      <c r="H390" t="n">
+        <v>0</v>
       </c>
       <c r="I390" t="inlineStr">
         <is>
@@ -78023,15 +77435,11 @@
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr"/>
-      <c r="G391" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H391" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G391" t="n">
+        <v>1</v>
+      </c>
+      <c r="H391" t="n">
+        <v>1</v>
       </c>
       <c r="I391" t="inlineStr">
         <is>
@@ -78131,15 +77539,11 @@
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr"/>
-      <c r="G392" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H392" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G392" t="n">
+        <v>1</v>
+      </c>
+      <c r="H392" t="n">
+        <v>0</v>
       </c>
       <c r="I392" t="inlineStr">
         <is>
@@ -78249,15 +77653,11 @@
         </is>
       </c>
       <c r="F393" t="inlineStr"/>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H393" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G393" t="n">
+        <v>0</v>
+      </c>
+      <c r="H393" t="n">
+        <v>1</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -78358,15 +77758,11 @@
       <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr"/>
       <c r="F394" t="inlineStr"/>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H394" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G394" t="n">
+        <v>1</v>
+      </c>
+      <c r="H394" t="n">
+        <v>1</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -78466,15 +77862,11 @@
       <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr"/>
-      <c r="G395" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H395" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G395" t="n">
+        <v>0</v>
+      </c>
+      <c r="H395" t="n">
+        <v>0</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
@@ -78574,15 +77966,11 @@
       <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr"/>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H396" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G396" t="n">
+        <v>2</v>
+      </c>
+      <c r="H396" t="n">
+        <v>1</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
@@ -78683,15 +78071,11 @@
       <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr"/>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H397" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G397" t="n">
+        <v>2</v>
+      </c>
+      <c r="H397" t="n">
+        <v>1</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
@@ -78792,15 +78176,11 @@
       <c r="D398" t="inlineStr"/>
       <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr"/>
-      <c r="G398" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H398" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G398" t="n">
+        <v>1</v>
+      </c>
+      <c r="H398" t="n">
+        <v>0</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
@@ -78901,15 +78281,11 @@
       <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr"/>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H399" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G399" t="n">
+        <v>3</v>
+      </c>
+      <c r="H399" t="n">
+        <v>1</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
@@ -79010,15 +78386,11 @@
       <c r="D400" t="inlineStr"/>
       <c r="E400" t="inlineStr"/>
       <c r="F400" t="inlineStr"/>
-      <c r="G400" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H400" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G400" t="n">
+        <v>3</v>
+      </c>
+      <c r="H400" t="n">
+        <v>2</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
@@ -79119,15 +78491,11 @@
       <c r="D401" t="inlineStr"/>
       <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr"/>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H401" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G401" t="n">
+        <v>2</v>
+      </c>
+      <c r="H401" t="n">
+        <v>1</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
@@ -79228,15 +78596,11 @@
       <c r="D402" t="inlineStr"/>
       <c r="E402" t="inlineStr"/>
       <c r="F402" t="inlineStr"/>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H402" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G402" t="n">
+        <v>6</v>
+      </c>
+      <c r="H402" t="n">
+        <v>2</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
@@ -79337,15 +78701,11 @@
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr"/>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H403" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="G403" t="n">
+        <v>0</v>
+      </c>
+      <c r="H403" t="n">
+        <v>5</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
@@ -79446,15 +78806,11 @@
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr"/>
-      <c r="G404" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H404" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G404" t="n">
+        <v>2</v>
+      </c>
+      <c r="H404" t="n">
+        <v>2</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
@@ -79554,15 +78910,11 @@
       <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr"/>
-      <c r="G405" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H405" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G405" t="n">
+        <v>1</v>
+      </c>
+      <c r="H405" t="n">
+        <v>0</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
@@ -79663,15 +79015,11 @@
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr"/>
       <c r="F406" t="inlineStr"/>
-      <c r="G406" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H406" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G406" t="n">
+        <v>1</v>
+      </c>
+      <c r="H406" t="n">
+        <v>1</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -79771,15 +79119,11 @@
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr"/>
       <c r="F407" t="inlineStr"/>
-      <c r="G407" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H407" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="G407" t="n">
+        <v>0</v>
+      </c>
+      <c r="H407" t="n">
+        <v>5</v>
       </c>
       <c r="I407" t="inlineStr">
         <is>
@@ -79889,15 +79233,11 @@
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
-      <c r="G408" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H408" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G408" t="n">
+        <v>3</v>
+      </c>
+      <c r="H408" t="n">
+        <v>3</v>
       </c>
       <c r="I408" t="inlineStr">
         <is>
@@ -79997,15 +79337,11 @@
       <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr"/>
-      <c r="G409" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H409" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G409" t="n">
+        <v>5</v>
+      </c>
+      <c r="H409" t="n">
+        <v>1</v>
       </c>
       <c r="I409" t="inlineStr">
         <is>
@@ -80106,15 +79442,11 @@
       <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr"/>
-      <c r="G410" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H410" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G410" t="n">
+        <v>2</v>
+      </c>
+      <c r="H410" t="n">
+        <v>4</v>
       </c>
       <c r="I410" t="inlineStr">
         <is>
@@ -80215,15 +79547,11 @@
       <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr"/>
       <c r="F411" t="inlineStr"/>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H411" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G411" t="n">
+        <v>2</v>
+      </c>
+      <c r="H411" t="n">
+        <v>1</v>
       </c>
       <c r="I411" t="inlineStr">
         <is>
@@ -80324,15 +79652,11 @@
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr"/>
       <c r="F412" t="inlineStr"/>
-      <c r="G412" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H412" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G412" t="n">
+        <v>0</v>
+      </c>
+      <c r="H412" t="n">
+        <v>2</v>
       </c>
       <c r="I412" t="inlineStr">
         <is>
@@ -80433,15 +79757,11 @@
       <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr"/>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G413" t="n">
+        <v>2</v>
+      </c>
+      <c r="H413" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="inlineStr">
         <is>
@@ -80542,15 +79862,11 @@
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="inlineStr"/>
-      <c r="G414" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H414" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G414" t="n">
+        <v>1</v>
+      </c>
+      <c r="H414" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="inlineStr">
         <is>
@@ -80651,15 +79967,11 @@
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr"/>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H415" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G415" t="n">
+        <v>4</v>
+      </c>
+      <c r="H415" t="n">
+        <v>0</v>
       </c>
       <c r="I415" t="inlineStr">
         <is>
@@ -80760,15 +80072,11 @@
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr"/>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H416" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G416" t="n">
+        <v>1</v>
+      </c>
+      <c r="H416" t="n">
+        <v>0</v>
       </c>
       <c r="I416" t="inlineStr">
         <is>
@@ -80869,15 +80177,11 @@
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr"/>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H417" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G417" t="n">
+        <v>3</v>
+      </c>
+      <c r="H417" t="n">
+        <v>0</v>
       </c>
       <c r="I417" t="inlineStr">
         <is>
@@ -80978,15 +80282,11 @@
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr"/>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H418" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G418" t="n">
+        <v>0</v>
+      </c>
+      <c r="H418" t="n">
+        <v>0</v>
       </c>
       <c r="I418" t="inlineStr">
         <is>
@@ -81086,15 +80386,11 @@
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr"/>
-      <c r="G419" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H419" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G419" t="n">
+        <v>1</v>
+      </c>
+      <c r="H419" t="n">
+        <v>1</v>
       </c>
       <c r="I419" t="inlineStr">
         <is>
@@ -81194,15 +80490,11 @@
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="inlineStr"/>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H420" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G420" t="n">
+        <v>1</v>
+      </c>
+      <c r="H420" t="n">
+        <v>1</v>
       </c>
       <c r="I420" t="inlineStr">
         <is>
@@ -81302,15 +80594,11 @@
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr"/>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H421" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G421" t="n">
+        <v>0</v>
+      </c>
+      <c r="H421" t="n">
+        <v>0</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
@@ -81410,15 +80698,11 @@
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="inlineStr"/>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H422" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G422" t="n">
+        <v>0</v>
+      </c>
+      <c r="H422" t="n">
+        <v>2</v>
       </c>
       <c r="I422" t="inlineStr">
         <is>
@@ -81519,15 +80803,11 @@
       <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr"/>
       <c r="F423" t="inlineStr"/>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H423" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G423" t="n">
+        <v>2</v>
+      </c>
+      <c r="H423" t="n">
+        <v>0</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -81628,15 +80908,11 @@
       <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr"/>
-      <c r="G424" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H424" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G424" t="n">
+        <v>3</v>
+      </c>
+      <c r="H424" t="n">
+        <v>1</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
@@ -81737,15 +81013,11 @@
       <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr"/>
       <c r="F425" t="inlineStr"/>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H425" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G425" t="n">
+        <v>3</v>
+      </c>
+      <c r="H425" t="n">
+        <v>0</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
@@ -81846,15 +81118,11 @@
       <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr"/>
       <c r="F426" t="inlineStr"/>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H426" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G426" t="n">
+        <v>0</v>
+      </c>
+      <c r="H426" t="n">
+        <v>1</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
@@ -81955,15 +81223,11 @@
       <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr"/>
       <c r="F427" t="inlineStr"/>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H427" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G427" t="n">
+        <v>3</v>
+      </c>
+      <c r="H427" t="n">
+        <v>0</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
@@ -82064,15 +81328,11 @@
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr"/>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H428" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G428" t="n">
+        <v>0</v>
+      </c>
+      <c r="H428" t="n">
+        <v>2</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -82182,15 +81442,11 @@
         </is>
       </c>
       <c r="F429" t="inlineStr"/>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H429" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G429" t="n">
+        <v>4</v>
+      </c>
+      <c r="H429" t="n">
+        <v>0</v>
       </c>
       <c r="I429" t="inlineStr">
         <is>
@@ -82291,15 +81547,11 @@
       <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr"/>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H430" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G430" t="n">
+        <v>1</v>
+      </c>
+      <c r="H430" t="n">
+        <v>0</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
@@ -82400,15 +81652,11 @@
       <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr"/>
       <c r="F431" t="inlineStr"/>
-      <c r="G431" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H431" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G431" t="n">
+        <v>2</v>
+      </c>
+      <c r="H431" t="n">
+        <v>1</v>
       </c>
       <c r="I431" t="inlineStr">
         <is>
@@ -82509,15 +81757,11 @@
       <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr"/>
       <c r="F432" t="inlineStr"/>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H432" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G432" t="n">
+        <v>1</v>
+      </c>
+      <c r="H432" t="n">
+        <v>4</v>
       </c>
       <c r="I432" t="inlineStr">
         <is>
@@ -82618,15 +81862,11 @@
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr"/>
       <c r="F433" t="inlineStr"/>
-      <c r="G433" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H433" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G433" t="n">
+        <v>0</v>
+      </c>
+      <c r="H433" t="n">
+        <v>0</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
@@ -82726,15 +81966,11 @@
       <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr"/>
       <c r="F434" t="inlineStr"/>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H434" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G434" t="n">
+        <v>1</v>
+      </c>
+      <c r="H434" t="n">
+        <v>1</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
@@ -82834,15 +82070,11 @@
       <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr"/>
       <c r="F435" t="inlineStr"/>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H435" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G435" t="n">
+        <v>2</v>
+      </c>
+      <c r="H435" t="n">
+        <v>0</v>
       </c>
       <c r="I435" t="inlineStr">
         <is>
@@ -82943,15 +82175,11 @@
       <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr"/>
       <c r="F436" t="inlineStr"/>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H436" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G436" t="n">
+        <v>4</v>
+      </c>
+      <c r="H436" t="n">
+        <v>1</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
@@ -83052,15 +82280,11 @@
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr"/>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H437" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G437" t="n">
+        <v>3</v>
+      </c>
+      <c r="H437" t="n">
+        <v>1</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
@@ -83161,15 +82385,11 @@
       <c r="D438" t="inlineStr"/>
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr"/>
-      <c r="G438" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G438" t="n">
+        <v>6</v>
+      </c>
+      <c r="H438" t="n">
+        <v>2</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
@@ -83270,15 +82490,11 @@
       <c r="D439" t="inlineStr"/>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr"/>
-      <c r="G439" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H439" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G439" t="n">
+        <v>0</v>
+      </c>
+      <c r="H439" t="n">
+        <v>1</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
@@ -83379,15 +82595,11 @@
       <c r="D440" t="inlineStr"/>
       <c r="E440" t="inlineStr"/>
       <c r="F440" t="inlineStr"/>
-      <c r="G440" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H440" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G440" t="n">
+        <v>0</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
@@ -83487,15 +82699,11 @@
       <c r="D441" t="inlineStr"/>
       <c r="E441" t="inlineStr"/>
       <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H441" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="G441" t="n">
+        <v>1</v>
+      </c>
+      <c r="H441" t="n">
+        <v>6</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
@@ -83596,15 +82804,11 @@
       <c r="D442" t="inlineStr"/>
       <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr"/>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H442" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G442" t="n">
+        <v>3</v>
+      </c>
+      <c r="H442" t="n">
+        <v>2</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
@@ -83705,15 +82909,11 @@
       <c r="D443" t="inlineStr"/>
       <c r="E443" t="inlineStr"/>
       <c r="F443" t="inlineStr"/>
-      <c r="G443" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H443" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G443" t="n">
+        <v>5</v>
+      </c>
+      <c r="H443" t="n">
+        <v>0</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
@@ -83814,15 +83014,11 @@
       <c r="D444" t="inlineStr"/>
       <c r="E444" t="inlineStr"/>
       <c r="F444" t="inlineStr"/>
-      <c r="G444" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H444" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G444" t="n">
+        <v>1</v>
+      </c>
+      <c r="H444" t="n">
+        <v>0</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
@@ -83923,15 +83119,11 @@
       <c r="D445" t="inlineStr"/>
       <c r="E445" t="inlineStr"/>
       <c r="F445" t="inlineStr"/>
-      <c r="G445" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H445" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G445" t="n">
+        <v>2</v>
+      </c>
+      <c r="H445" t="n">
+        <v>2</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
@@ -84031,15 +83223,11 @@
       <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr"/>
-      <c r="G446" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H446" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G446" t="n">
+        <v>2</v>
+      </c>
+      <c r="H446" t="n">
+        <v>3</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
@@ -84140,15 +83328,11 @@
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="inlineStr"/>
-      <c r="G447" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H447" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G447" t="n">
+        <v>2</v>
+      </c>
+      <c r="H447" t="n">
+        <v>1</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
@@ -84249,15 +83433,11 @@
       <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr"/>
-      <c r="G448" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H448" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G448" t="n">
+        <v>2</v>
+      </c>
+      <c r="H448" t="n">
+        <v>1</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
@@ -84358,15 +83538,11 @@
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="inlineStr"/>
-      <c r="G449" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H449" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G449" t="n">
+        <v>1</v>
+      </c>
+      <c r="H449" t="n">
+        <v>1</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
@@ -84466,15 +83642,11 @@
       <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr"/>
       <c r="F450" t="inlineStr"/>
-      <c r="G450" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H450" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G450" t="n">
+        <v>4</v>
+      </c>
+      <c r="H450" t="n">
+        <v>1</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
@@ -84575,15 +83747,11 @@
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="inlineStr"/>
-      <c r="G451" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H451" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G451" t="n">
+        <v>0</v>
+      </c>
+      <c r="H451" t="n">
+        <v>1</v>
       </c>
       <c r="I451" t="inlineStr">
         <is>
@@ -84693,15 +83861,11 @@
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
-      <c r="G452" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H452" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G452" t="n">
+        <v>3</v>
+      </c>
+      <c r="H452" t="n">
+        <v>1</v>
       </c>
       <c r="I452" t="inlineStr">
         <is>
@@ -84802,15 +83966,11 @@
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr"/>
-      <c r="G453" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H453" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G453" t="n">
+        <v>3</v>
+      </c>
+      <c r="H453" t="n">
+        <v>2</v>
       </c>
       <c r="I453" t="inlineStr">
         <is>
@@ -84911,15 +84071,11 @@
       <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr"/>
-      <c r="G454" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H454" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G454" t="n">
+        <v>1</v>
+      </c>
+      <c r="H454" t="n">
+        <v>1</v>
       </c>
       <c r="I454" t="inlineStr">
         <is>
@@ -85019,15 +84175,11 @@
       <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr"/>
       <c r="F455" t="inlineStr"/>
-      <c r="G455" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H455" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G455" t="n">
+        <v>5</v>
+      </c>
+      <c r="H455" t="n">
+        <v>0</v>
       </c>
       <c r="I455" t="inlineStr">
         <is>
@@ -85137,15 +84289,11 @@
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
-      <c r="G456" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H456" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G456" t="n">
+        <v>1</v>
+      </c>
+      <c r="H456" t="n">
+        <v>1</v>
       </c>
       <c r="I456" t="inlineStr">
         <is>
@@ -85245,15 +84393,11 @@
       <c r="D457" t="inlineStr"/>
       <c r="E457" t="inlineStr"/>
       <c r="F457" t="inlineStr"/>
-      <c r="G457" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H457" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G457" t="n">
+        <v>2</v>
+      </c>
+      <c r="H457" t="n">
+        <v>2</v>
       </c>
       <c r="I457" t="inlineStr">
         <is>
@@ -85353,15 +84497,11 @@
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr"/>
       <c r="F458" t="inlineStr"/>
-      <c r="G458" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H458" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G458" t="n">
+        <v>0</v>
+      </c>
+      <c r="H458" t="n">
+        <v>0</v>
       </c>
       <c r="I458" t="inlineStr">
         <is>
@@ -85461,15 +84601,11 @@
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="inlineStr"/>
-      <c r="G459" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H459" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G459" t="n">
+        <v>2</v>
+      </c>
+      <c r="H459" t="n">
+        <v>2</v>
       </c>
       <c r="I459" t="inlineStr">
         <is>
@@ -85569,15 +84705,11 @@
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="inlineStr"/>
-      <c r="G460" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H460" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G460" t="n">
+        <v>1</v>
+      </c>
+      <c r="H460" t="n">
+        <v>2</v>
       </c>
       <c r="I460" t="inlineStr">
         <is>
@@ -85678,15 +84810,11 @@
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr"/>
-      <c r="G461" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H461" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G461" t="n">
+        <v>1</v>
+      </c>
+      <c r="H461" t="n">
+        <v>0</v>
       </c>
       <c r="I461" t="inlineStr">
         <is>
@@ -85787,15 +84915,11 @@
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
-      <c r="G462" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H462" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G462" t="n">
+        <v>2</v>
+      </c>
+      <c r="H462" t="n">
+        <v>3</v>
       </c>
       <c r="I462" t="inlineStr">
         <is>
@@ -85896,15 +85020,11 @@
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
-      <c r="G463" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H463" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G463" t="n">
+        <v>1</v>
+      </c>
+      <c r="H463" t="n">
+        <v>1</v>
       </c>
       <c r="I463" t="inlineStr">
         <is>
@@ -86004,15 +85124,11 @@
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
-      <c r="G464" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H464" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G464" t="n">
+        <v>0</v>
+      </c>
+      <c r="H464" t="n">
+        <v>3</v>
       </c>
       <c r="I464" t="inlineStr">
         <is>
@@ -86113,15 +85229,11 @@
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr"/>
       <c r="F465" t="inlineStr"/>
-      <c r="G465" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H465" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G465" t="n">
+        <v>3</v>
+      </c>
+      <c r="H465" t="n">
+        <v>0</v>
       </c>
       <c r="I465" t="inlineStr">
         <is>
@@ -86222,15 +85334,11 @@
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr"/>
       <c r="F466" t="inlineStr"/>
-      <c r="G466" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H466" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G466" t="n">
+        <v>0</v>
+      </c>
+      <c r="H466" t="n">
+        <v>1</v>
       </c>
       <c r="I466" t="inlineStr">
         <is>
@@ -86331,15 +85439,11 @@
       <c r="D467" t="inlineStr"/>
       <c r="E467" t="inlineStr"/>
       <c r="F467" t="inlineStr"/>
-      <c r="G467" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H467" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G467" t="n">
+        <v>0</v>
+      </c>
+      <c r="H467" t="n">
+        <v>4</v>
       </c>
       <c r="I467" t="inlineStr">
         <is>
@@ -86440,15 +85544,11 @@
       <c r="D468" t="inlineStr"/>
       <c r="E468" t="inlineStr"/>
       <c r="F468" t="inlineStr"/>
-      <c r="G468" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H468" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G468" t="n">
+        <v>2</v>
+      </c>
+      <c r="H468" t="n">
+        <v>2</v>
       </c>
       <c r="I468" t="inlineStr">
         <is>
@@ -86548,15 +85648,11 @@
       <c r="D469" t="inlineStr"/>
       <c r="E469" t="inlineStr"/>
       <c r="F469" t="inlineStr"/>
-      <c r="G469" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H469" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G469" t="n">
+        <v>0</v>
+      </c>
+      <c r="H469" t="n">
+        <v>3</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
@@ -86657,15 +85753,11 @@
       <c r="D470" t="inlineStr"/>
       <c r="E470" t="inlineStr"/>
       <c r="F470" t="inlineStr"/>
-      <c r="G470" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H470" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G470" t="n">
+        <v>4</v>
+      </c>
+      <c r="H470" t="n">
+        <v>0</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
@@ -86766,15 +85858,11 @@
       <c r="D471" t="inlineStr"/>
       <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr"/>
-      <c r="G471" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H471" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G471" t="n">
+        <v>0</v>
+      </c>
+      <c r="H471" t="n">
+        <v>2</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
@@ -86875,15 +85963,11 @@
       <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr"/>
       <c r="F472" t="inlineStr"/>
-      <c r="G472" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H472" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G472" t="n">
+        <v>4</v>
+      </c>
+      <c r="H472" t="n">
+        <v>2</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
@@ -86984,15 +86068,11 @@
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr"/>
       <c r="F473" t="inlineStr"/>
-      <c r="G473" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H473" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G473" t="n">
+        <v>3</v>
+      </c>
+      <c r="H473" t="n">
+        <v>1</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
@@ -87093,15 +86173,11 @@
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr"/>
       <c r="F474" t="inlineStr"/>
-      <c r="G474" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H474" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G474" t="n">
+        <v>0</v>
+      </c>
+      <c r="H474" t="n">
+        <v>2</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
@@ -87202,15 +86278,11 @@
       <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr"/>
       <c r="F475" t="inlineStr"/>
-      <c r="G475" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H475" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G475" t="n">
+        <v>1</v>
+      </c>
+      <c r="H475" t="n">
+        <v>1</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
@@ -87310,15 +86382,11 @@
       <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr"/>
       <c r="F476" t="inlineStr"/>
-      <c r="G476" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H476" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G476" t="n">
+        <v>1</v>
+      </c>
+      <c r="H476" t="n">
+        <v>0</v>
       </c>
       <c r="I476" t="inlineStr">
         <is>
@@ -87419,15 +86487,11 @@
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr"/>
       <c r="F477" t="inlineStr"/>
-      <c r="G477" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H477" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G477" t="n">
+        <v>1</v>
+      </c>
+      <c r="H477" t="n">
+        <v>0</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -87528,15 +86592,11 @@
       <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr"/>
       <c r="F478" t="inlineStr"/>
-      <c r="G478" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H478" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G478" t="n">
+        <v>3</v>
+      </c>
+      <c r="H478" t="n">
+        <v>2</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
@@ -87637,15 +86697,11 @@
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr"/>
       <c r="F479" t="inlineStr"/>
-      <c r="G479" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H479" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G479" t="n">
+        <v>0</v>
+      </c>
+      <c r="H479" t="n">
+        <v>1</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
@@ -87746,15 +86802,11 @@
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr"/>
       <c r="F480" t="inlineStr"/>
-      <c r="G480" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H480" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G480" t="n">
+        <v>1</v>
+      </c>
+      <c r="H480" t="n">
+        <v>1</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
@@ -87872,15 +86924,11 @@
           <t>29 270</t>
         </is>
       </c>
-      <c r="G481" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H481" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G481" t="n">
+        <v>3</v>
+      </c>
+      <c r="H481" t="n">
+        <v>0</v>
       </c>
       <c r="I481" t="inlineStr">
         <is>
@@ -87914,121 +86962,77 @@
           <t>64%</t>
         </is>
       </c>
-      <c r="Q481" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R481" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S481" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T481" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U481" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V481" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q481" t="n">
+        <v>21</v>
+      </c>
+      <c r="R481" t="n">
+        <v>15</v>
+      </c>
+      <c r="S481" t="n">
+        <v>7</v>
+      </c>
+      <c r="T481" t="n">
+        <v>6</v>
+      </c>
+      <c r="U481" t="n">
+        <v>8</v>
+      </c>
+      <c r="V481" t="n">
+        <v>3</v>
       </c>
       <c r="W481" t="inlineStr"/>
       <c r="X481" t="inlineStr"/>
-      <c r="Y481" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z481" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA481" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB481" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC481" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AD481" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AE481" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AF481" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG481" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH481" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI481" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ481" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y481" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z481" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA481" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB481" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC481" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD481" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE481" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF481" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG481" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH481" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI481" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ481" t="n">
+        <v>0</v>
       </c>
       <c r="AK481" t="inlineStr"/>
       <c r="AL481" t="inlineStr"/>
       <c r="AM481" t="inlineStr"/>
       <c r="AN481" t="inlineStr"/>
-      <c r="AO481" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="AP481" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="AQ481" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AR481" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="AO481" t="n">
+        <v>67</v>
+      </c>
+      <c r="AP481" t="n">
+        <v>139</v>
+      </c>
+      <c r="AQ481" t="n">
+        <v>45</v>
+      </c>
+      <c r="AR481" t="n">
+        <v>62</v>
       </c>
       <c r="AS481" t="inlineStr"/>
       <c r="AT481" t="inlineStr"/>
@@ -88066,15 +87070,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC481" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BD481" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="BC481" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD481" t="n">
+        <v>6</v>
       </c>
       <c r="BE481" t="inlineStr"/>
       <c r="BF481" t="inlineStr"/>
@@ -88118,15 +87118,11 @@
           <t>36 517</t>
         </is>
       </c>
-      <c r="G482" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H482" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G482" t="n">
+        <v>2</v>
+      </c>
+      <c r="H482" t="n">
+        <v>0</v>
       </c>
       <c r="I482" t="inlineStr">
         <is>
@@ -88160,121 +87156,77 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q482" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R482" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S482" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T482" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U482" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V482" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q482" t="n">
+        <v>17</v>
+      </c>
+      <c r="R482" t="n">
+        <v>9</v>
+      </c>
+      <c r="S482" t="n">
+        <v>5</v>
+      </c>
+      <c r="T482" t="n">
+        <v>2</v>
+      </c>
+      <c r="U482" t="n">
+        <v>4</v>
+      </c>
+      <c r="V482" t="n">
+        <v>4</v>
       </c>
       <c r="W482" t="inlineStr"/>
       <c r="X482" t="inlineStr"/>
-      <c r="Y482" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z482" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA482" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB482" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC482" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AD482" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AE482" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF482" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG482" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH482" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AI482" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ482" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y482" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z482" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA482" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB482" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC482" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD482" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE482" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF482" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG482" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH482" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI482" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ482" t="n">
+        <v>1</v>
       </c>
       <c r="AK482" t="inlineStr"/>
       <c r="AL482" t="inlineStr"/>
       <c r="AM482" t="inlineStr"/>
       <c r="AN482" t="inlineStr"/>
-      <c r="AO482" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="AP482" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="AQ482" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="AR482" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="AO482" t="n">
+        <v>127</v>
+      </c>
+      <c r="AP482" t="n">
+        <v>87</v>
+      </c>
+      <c r="AQ482" t="n">
+        <v>46</v>
+      </c>
+      <c r="AR482" t="n">
+        <v>42</v>
       </c>
       <c r="AS482" t="inlineStr"/>
       <c r="AT482" t="inlineStr"/>
@@ -88312,15 +87264,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC482" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BD482" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="BC482" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD482" t="n">
+        <v>3</v>
       </c>
       <c r="BE482" t="inlineStr"/>
       <c r="BF482" t="inlineStr"/>
@@ -88364,15 +87312,11 @@
           <t>14 905</t>
         </is>
       </c>
-      <c r="G483" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H483" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G483" t="n">
+        <v>3</v>
+      </c>
+      <c r="H483" t="n">
+        <v>0</v>
       </c>
       <c r="I483" t="inlineStr">
         <is>
@@ -88406,121 +87350,77 @@
           <t>59%</t>
         </is>
       </c>
-      <c r="Q483" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R483" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S483" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T483" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U483" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V483" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q483" t="n">
+        <v>19</v>
+      </c>
+      <c r="R483" t="n">
+        <v>4</v>
+      </c>
+      <c r="S483" t="n">
+        <v>4</v>
+      </c>
+      <c r="T483" t="n">
+        <v>1</v>
+      </c>
+      <c r="U483" t="n">
+        <v>8</v>
+      </c>
+      <c r="V483" t="n">
+        <v>1</v>
       </c>
       <c r="W483" t="inlineStr"/>
       <c r="X483" t="inlineStr"/>
-      <c r="Y483" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z483" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA483" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB483" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC483" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AD483" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AE483" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF483" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG483" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH483" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI483" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ483" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y483" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z483" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA483" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB483" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC483" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD483" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE483" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF483" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG483" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH483" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI483" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ483" t="n">
+        <v>1</v>
       </c>
       <c r="AK483" t="inlineStr"/>
       <c r="AL483" t="inlineStr"/>
       <c r="AM483" t="inlineStr"/>
       <c r="AN483" t="inlineStr"/>
-      <c r="AO483" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="AP483" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AQ483" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AR483" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="AO483" t="n">
+        <v>123</v>
+      </c>
+      <c r="AP483" t="n">
+        <v>106</v>
+      </c>
+      <c r="AQ483" t="n">
+        <v>40</v>
+      </c>
+      <c r="AR483" t="n">
+        <v>53</v>
       </c>
       <c r="AS483" t="inlineStr"/>
       <c r="AT483" t="inlineStr"/>
@@ -88558,15 +87458,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC483" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BD483" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="BC483" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD483" t="n">
+        <v>2</v>
       </c>
       <c r="BE483" t="inlineStr"/>
       <c r="BF483" t="inlineStr"/>
@@ -88610,15 +87506,11 @@
           <t>11 403</t>
         </is>
       </c>
-      <c r="G484" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H484" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G484" t="n">
+        <v>3</v>
+      </c>
+      <c r="H484" t="n">
+        <v>1</v>
       </c>
       <c r="I484" t="inlineStr">
         <is>
@@ -88652,121 +87544,77 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q484" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R484" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S484" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T484" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U484" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V484" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q484" t="n">
+        <v>6</v>
+      </c>
+      <c r="R484" t="n">
+        <v>9</v>
+      </c>
+      <c r="S484" t="n">
+        <v>3</v>
+      </c>
+      <c r="T484" t="n">
+        <v>4</v>
+      </c>
+      <c r="U484" t="n">
+        <v>2</v>
+      </c>
+      <c r="V484" t="n">
+        <v>4</v>
       </c>
       <c r="W484" t="inlineStr"/>
       <c r="X484" t="inlineStr"/>
-      <c r="Y484" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z484" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA484" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB484" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC484" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD484" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AE484" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF484" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG484" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH484" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AI484" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ484" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Y484" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z484" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA484" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB484" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC484" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD484" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE484" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF484" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG484" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH484" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI484" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ484" t="n">
+        <v>5</v>
       </c>
       <c r="AK484" t="inlineStr"/>
       <c r="AL484" t="inlineStr"/>
       <c r="AM484" t="inlineStr"/>
       <c r="AN484" t="inlineStr"/>
-      <c r="AO484" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="AP484" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AQ484" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AR484" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="AO484" t="n">
+        <v>74</v>
+      </c>
+      <c r="AP484" t="n">
+        <v>116</v>
+      </c>
+      <c r="AQ484" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR484" t="n">
+        <v>42</v>
       </c>
       <c r="AS484" t="inlineStr"/>
       <c r="AT484" t="inlineStr"/>
@@ -88804,25 +87652,17 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC484" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD484" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BE484" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF484" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC484" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD484" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE484" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF484" t="n">
+        <v>1</v>
       </c>
       <c r="BG484" t="inlineStr"/>
       <c r="BH484" t="inlineStr"/>
@@ -88864,15 +87704,11 @@
           <t>16 934</t>
         </is>
       </c>
-      <c r="G485" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H485" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G485" t="n">
+        <v>0</v>
+      </c>
+      <c r="H485" t="n">
+        <v>1</v>
       </c>
       <c r="I485" t="inlineStr">
         <is>
@@ -88906,121 +87742,77 @@
           <t>43%</t>
         </is>
       </c>
-      <c r="Q485" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R485" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S485" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T485" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U485" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V485" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q485" t="n">
+        <v>15</v>
+      </c>
+      <c r="R485" t="n">
+        <v>16</v>
+      </c>
+      <c r="S485" t="n">
+        <v>7</v>
+      </c>
+      <c r="T485" t="n">
+        <v>8</v>
+      </c>
+      <c r="U485" t="n">
+        <v>5</v>
+      </c>
+      <c r="V485" t="n">
+        <v>2</v>
       </c>
       <c r="W485" t="inlineStr"/>
       <c r="X485" t="inlineStr"/>
-      <c r="Y485" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z485" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA485" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB485" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC485" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AD485" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AE485" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AF485" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AG485" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH485" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AI485" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ485" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y485" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z485" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA485" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB485" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC485" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD485" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE485" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF485" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG485" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH485" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI485" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ485" t="n">
+        <v>3</v>
       </c>
       <c r="AK485" t="inlineStr"/>
       <c r="AL485" t="inlineStr"/>
       <c r="AM485" t="inlineStr"/>
       <c r="AN485" t="inlineStr"/>
-      <c r="AO485" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="AP485" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AQ485" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AR485" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="AO485" t="n">
+        <v>94</v>
+      </c>
+      <c r="AP485" t="n">
+        <v>70</v>
+      </c>
+      <c r="AQ485" t="n">
+        <v>40</v>
+      </c>
+      <c r="AR485" t="n">
+        <v>51</v>
       </c>
       <c r="AS485" t="inlineStr"/>
       <c r="AT485" t="inlineStr"/>
@@ -89058,15 +87850,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC485" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BD485" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="BC485" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD485" t="n">
+        <v>6</v>
       </c>
       <c r="BE485" t="inlineStr"/>
       <c r="BF485" t="inlineStr"/>
@@ -89110,15 +87898,11 @@
           <t>20 231</t>
         </is>
       </c>
-      <c r="G486" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H486" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G486" t="n">
+        <v>1</v>
+      </c>
+      <c r="H486" t="n">
+        <v>3</v>
       </c>
       <c r="I486" t="inlineStr">
         <is>
@@ -89152,121 +87936,77 @@
           <t>43%</t>
         </is>
       </c>
-      <c r="Q486" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R486" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S486" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T486" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U486" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V486" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q486" t="n">
+        <v>4</v>
+      </c>
+      <c r="R486" t="n">
+        <v>8</v>
+      </c>
+      <c r="S486" t="n">
+        <v>3</v>
+      </c>
+      <c r="T486" t="n">
+        <v>4</v>
+      </c>
+      <c r="U486" t="n">
+        <v>1</v>
+      </c>
+      <c r="V486" t="n">
+        <v>1</v>
       </c>
       <c r="W486" t="inlineStr"/>
       <c r="X486" t="inlineStr"/>
-      <c r="Y486" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z486" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA486" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB486" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC486" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AD486" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AE486" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF486" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG486" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH486" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI486" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ486" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y486" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z486" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA486" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB486" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC486" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD486" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE486" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF486" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG486" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH486" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI486" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ486" t="n">
+        <v>1</v>
       </c>
       <c r="AK486" t="inlineStr"/>
       <c r="AL486" t="inlineStr"/>
       <c r="AM486" t="inlineStr"/>
       <c r="AN486" t="inlineStr"/>
-      <c r="AO486" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AP486" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AQ486" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="AR486" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="AO486" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP486" t="n">
+        <v>95</v>
+      </c>
+      <c r="AQ486" t="n">
+        <v>49</v>
+      </c>
+      <c r="AR486" t="n">
+        <v>45</v>
       </c>
       <c r="AS486" t="inlineStr"/>
       <c r="AT486" t="inlineStr"/>
@@ -89304,15 +88044,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC486" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD486" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="BC486" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD486" t="n">
+        <v>3</v>
       </c>
       <c r="BE486" t="inlineStr"/>
       <c r="BF486" t="inlineStr"/>
@@ -89356,15 +88092,11 @@
           <t>24 175</t>
         </is>
       </c>
-      <c r="G487" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H487" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G487" t="n">
+        <v>1</v>
+      </c>
+      <c r="H487" t="n">
+        <v>0</v>
       </c>
       <c r="I487" t="inlineStr">
         <is>
@@ -89398,121 +88130,77 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q487" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R487" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S487" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T487" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U487" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V487" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q487" t="n">
+        <v>14</v>
+      </c>
+      <c r="R487" t="n">
+        <v>6</v>
+      </c>
+      <c r="S487" t="n">
+        <v>5</v>
+      </c>
+      <c r="T487" t="n">
+        <v>2</v>
+      </c>
+      <c r="U487" t="n">
+        <v>6</v>
+      </c>
+      <c r="V487" t="n">
+        <v>0</v>
       </c>
       <c r="W487" t="inlineStr"/>
       <c r="X487" t="inlineStr"/>
-      <c r="Y487" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z487" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA487" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB487" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC487" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AD487" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AE487" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF487" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG487" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AH487" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI487" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ487" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y487" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z487" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA487" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB487" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC487" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD487" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE487" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF487" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG487" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH487" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI487" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ487" t="n">
+        <v>1</v>
       </c>
       <c r="AK487" t="inlineStr"/>
       <c r="AL487" t="inlineStr"/>
       <c r="AM487" t="inlineStr"/>
       <c r="AN487" t="inlineStr"/>
-      <c r="AO487" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="AP487" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AQ487" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="AR487" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="AO487" t="n">
+        <v>98</v>
+      </c>
+      <c r="AP487" t="n">
+        <v>90</v>
+      </c>
+      <c r="AQ487" t="n">
+        <v>54</v>
+      </c>
+      <c r="AR487" t="n">
+        <v>46</v>
       </c>
       <c r="AS487" t="inlineStr"/>
       <c r="AT487" t="inlineStr"/>
@@ -89550,15 +88238,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC487" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BD487" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="BC487" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD487" t="n">
+        <v>4</v>
       </c>
       <c r="BE487" t="inlineStr"/>
       <c r="BF487" t="inlineStr"/>
@@ -89602,15 +88286,11 @@
           <t>21 042</t>
         </is>
       </c>
-      <c r="G488" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H488" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G488" t="n">
+        <v>1</v>
+      </c>
+      <c r="H488" t="n">
+        <v>1</v>
       </c>
       <c r="I488" t="inlineStr">
         <is>
@@ -89644,121 +88324,77 @@
           <t>23%</t>
         </is>
       </c>
-      <c r="Q488" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R488" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S488" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T488" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U488" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V488" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Q488" t="n">
+        <v>16</v>
+      </c>
+      <c r="R488" t="n">
+        <v>11</v>
+      </c>
+      <c r="S488" t="n">
+        <v>3</v>
+      </c>
+      <c r="T488" t="n">
+        <v>3</v>
+      </c>
+      <c r="U488" t="n">
+        <v>10</v>
+      </c>
+      <c r="V488" t="n">
+        <v>7</v>
       </c>
       <c r="W488" t="inlineStr"/>
       <c r="X488" t="inlineStr"/>
-      <c r="Y488" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z488" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA488" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB488" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC488" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AD488" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AE488" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF488" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG488" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH488" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AI488" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ488" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Y488" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z488" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA488" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB488" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC488" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD488" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE488" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF488" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG488" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH488" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI488" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ488" t="n">
+        <v>7</v>
       </c>
       <c r="AK488" t="inlineStr"/>
       <c r="AL488" t="inlineStr"/>
       <c r="AM488" t="inlineStr"/>
       <c r="AN488" t="inlineStr"/>
-      <c r="AO488" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="AP488" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="AQ488" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AR488" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="AO488" t="n">
+        <v>146</v>
+      </c>
+      <c r="AP488" t="n">
+        <v>75</v>
+      </c>
+      <c r="AQ488" t="n">
+        <v>90</v>
+      </c>
+      <c r="AR488" t="n">
+        <v>8</v>
       </c>
       <c r="AS488" t="inlineStr"/>
       <c r="AT488" t="inlineStr"/>
@@ -89796,25 +88432,17 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC488" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BD488" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BE488" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF488" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC488" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD488" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE488" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF488" t="n">
+        <v>1</v>
       </c>
       <c r="BG488" t="inlineStr"/>
       <c r="BH488" t="inlineStr"/>
@@ -89856,15 +88484,11 @@
           <t>18 000</t>
         </is>
       </c>
-      <c r="G489" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H489" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G489" t="n">
+        <v>0</v>
+      </c>
+      <c r="H489" t="n">
+        <v>2</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -89898,121 +88522,77 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q489" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R489" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S489" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T489" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U489" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V489" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q489" t="n">
+        <v>12</v>
+      </c>
+      <c r="R489" t="n">
+        <v>11</v>
+      </c>
+      <c r="S489" t="n">
+        <v>3</v>
+      </c>
+      <c r="T489" t="n">
+        <v>6</v>
+      </c>
+      <c r="U489" t="n">
+        <v>5</v>
+      </c>
+      <c r="V489" t="n">
+        <v>4</v>
       </c>
       <c r="W489" t="inlineStr"/>
       <c r="X489" t="inlineStr"/>
-      <c r="Y489" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z489" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA489" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB489" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC489" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AD489" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AE489" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF489" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG489" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AH489" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI489" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ489" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Y489" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z489" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA489" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB489" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC489" t="n">
+        <v>33</v>
+      </c>
+      <c r="AD489" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE489" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF489" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG489" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH489" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI489" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ489" t="n">
+        <v>1</v>
       </c>
       <c r="AK489" t="inlineStr"/>
       <c r="AL489" t="inlineStr"/>
       <c r="AM489" t="inlineStr"/>
       <c r="AN489" t="inlineStr"/>
-      <c r="AO489" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="AP489" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="AQ489" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="AR489" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="AO489" t="n">
+        <v>88</v>
+      </c>
+      <c r="AP489" t="n">
+        <v>117</v>
+      </c>
+      <c r="AQ489" t="n">
+        <v>49</v>
+      </c>
+      <c r="AR489" t="n">
+        <v>38</v>
       </c>
       <c r="AS489" t="inlineStr"/>
       <c r="AT489" t="inlineStr"/>
@@ -90050,15 +88630,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC489" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BD489" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC489" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD489" t="n">
+        <v>1</v>
       </c>
       <c r="BE489" t="inlineStr"/>
       <c r="BF489" t="inlineStr"/>
@@ -90102,15 +88678,11 @@
           <t>27 353</t>
         </is>
       </c>
-      <c r="G490" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H490" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G490" t="n">
+        <v>0</v>
+      </c>
+      <c r="H490" t="n">
+        <v>1</v>
       </c>
       <c r="I490" t="inlineStr">
         <is>
@@ -90144,121 +88716,77 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="Q490" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R490" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S490" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T490" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U490" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V490" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q490" t="n">
+        <v>14</v>
+      </c>
+      <c r="R490" t="n">
+        <v>10</v>
+      </c>
+      <c r="S490" t="n">
+        <v>5</v>
+      </c>
+      <c r="T490" t="n">
+        <v>1</v>
+      </c>
+      <c r="U490" t="n">
+        <v>5</v>
+      </c>
+      <c r="V490" t="n">
+        <v>3</v>
       </c>
       <c r="W490" t="inlineStr"/>
       <c r="X490" t="inlineStr"/>
-      <c r="Y490" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z490" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA490" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB490" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC490" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AD490" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE490" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF490" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG490" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH490" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AI490" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ490" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Y490" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z490" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA490" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB490" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC490" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD490" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE490" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF490" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG490" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH490" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI490" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ490" t="n">
+        <v>3</v>
       </c>
       <c r="AK490" t="inlineStr"/>
       <c r="AL490" t="inlineStr"/>
       <c r="AM490" t="inlineStr"/>
       <c r="AN490" t="inlineStr"/>
-      <c r="AO490" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="AP490" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="AQ490" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="AR490" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="AO490" t="n">
+        <v>117</v>
+      </c>
+      <c r="AP490" t="n">
+        <v>124</v>
+      </c>
+      <c r="AQ490" t="n">
+        <v>63</v>
+      </c>
+      <c r="AR490" t="n">
+        <v>41</v>
       </c>
       <c r="AS490" t="inlineStr"/>
       <c r="AT490" t="inlineStr"/>
@@ -90296,15 +88824,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC490" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BD490" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="BC490" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD490" t="n">
+        <v>6</v>
       </c>
       <c r="BE490" t="inlineStr"/>
       <c r="BF490" t="inlineStr"/>
@@ -90315,6 +88839,1219 @@
       <c r="BK490" t="inlineStr"/>
       <c r="BL490" t="inlineStr"/>
     </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>z1q67ylB</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>01.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Taylor A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Old Trafford
+ (Manchester)</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>75 635</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>73 738</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>Manchester Utd</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T491" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U491" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V491" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W491" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X491" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y491" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z491" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA491" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB491" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC491" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AD491" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AE491" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF491" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG491" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH491" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI491" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ491" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK491" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="AL491" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="AM491" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AN491" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AO491" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AP491" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AQ491" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AR491" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AS491" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AT491" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AU491" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="AV491" t="inlineStr">
+        <is>
+          <t>ten hag erik</t>
+        </is>
+      </c>
+      <c r="AW491" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="AX491" t="inlineStr">
+        <is>
+          <t>slot arne</t>
+        </is>
+      </c>
+      <c r="AY491" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ491" t="n">
+        <v>481</v>
+      </c>
+      <c r="BA491" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB491" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC491" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD491" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE491" t="inlineStr"/>
+      <c r="BF491" t="inlineStr"/>
+      <c r="BG491" t="inlineStr"/>
+      <c r="BH491" t="inlineStr"/>
+      <c r="BI491" t="inlineStr"/>
+      <c r="BJ491" t="inlineStr"/>
+      <c r="BK491" t="inlineStr"/>
+      <c r="BL491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>tvOWhxZH</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>01.09.2024 09:30</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Gillett J.
+ (Aus)</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Stamford Bridge
+ (London)</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>40 341</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>39 298</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T492" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U492" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V492" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W492" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X492" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y492" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z492" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA492" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB492" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC492" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD492" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AE492" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF492" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG492" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH492" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI492" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ492" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK492" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="AL492" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="AM492" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AN492" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AO492" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="AP492" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AQ492" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AR492" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AS492" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AT492" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AU492" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="AV492" t="inlineStr">
+        <is>
+          <t>maresca enzo</t>
+        </is>
+      </c>
+      <c r="AW492" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="AX492" t="inlineStr">
+        <is>
+          <t>glasner oliver</t>
+        </is>
+      </c>
+      <c r="AY492" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ492" t="n">
+        <v>481</v>
+      </c>
+      <c r="BA492" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB492" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC492" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BD492" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BE492" t="inlineStr"/>
+      <c r="BF492" t="inlineStr"/>
+      <c r="BG492" t="inlineStr"/>
+      <c r="BH492" t="inlineStr"/>
+      <c r="BI492" t="inlineStr"/>
+      <c r="BJ492" t="inlineStr"/>
+      <c r="BK492" t="inlineStr"/>
+      <c r="BL492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>U11vkTXq</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>01.09.2024 09:30</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Jones R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>St. James' Park
+ (Newcastle)</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>52 305</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>52 211</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T493" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U493" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V493" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W493" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X493" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Y493" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z493" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA493" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB493" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC493" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD493" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE493" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF493" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG493" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH493" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI493" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ493" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK493" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="AL493" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="AM493" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AN493" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AO493" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AP493" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="AQ493" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AR493" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AS493" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AT493" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AU493" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="AV493" t="inlineStr">
+        <is>
+          <t>howe eddie</t>
+        </is>
+      </c>
+      <c r="AW493" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="AX493" t="inlineStr">
+        <is>
+          <t>postecoglou ange</t>
+        </is>
+      </c>
+      <c r="AY493" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ493" t="n">
+        <v>481</v>
+      </c>
+      <c r="BA493" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB493" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC493" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BD493" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BE493" t="inlineStr"/>
+      <c r="BF493" t="inlineStr"/>
+      <c r="BG493" t="inlineStr"/>
+      <c r="BH493" t="inlineStr"/>
+      <c r="BI493" t="inlineStr"/>
+      <c r="BJ493" t="inlineStr"/>
+      <c r="BK493" t="inlineStr"/>
+      <c r="BL493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>SWRIzxdS</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>01.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr"/>
+      <c r="D494" t="inlineStr"/>
+      <c r="E494" t="inlineStr"/>
+      <c r="F494" t="inlineStr"/>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>KY3WutAL</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>Great Yarmouth</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Io6VnVE8</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>Cheshunt
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr"/>
+      <c r="N494" t="inlineStr"/>
+      <c r="O494" t="inlineStr"/>
+      <c r="P494" t="inlineStr"/>
+      <c r="Q494" t="inlineStr"/>
+      <c r="R494" t="inlineStr"/>
+      <c r="S494" t="inlineStr"/>
+      <c r="T494" t="inlineStr"/>
+      <c r="U494" t="inlineStr"/>
+      <c r="V494" t="inlineStr"/>
+      <c r="W494" t="inlineStr"/>
+      <c r="X494" t="inlineStr"/>
+      <c r="Y494" t="inlineStr"/>
+      <c r="Z494" t="inlineStr"/>
+      <c r="AA494" t="inlineStr"/>
+      <c r="AB494" t="inlineStr"/>
+      <c r="AC494" t="inlineStr"/>
+      <c r="AD494" t="inlineStr"/>
+      <c r="AE494" t="inlineStr"/>
+      <c r="AF494" t="inlineStr"/>
+      <c r="AG494" t="inlineStr"/>
+      <c r="AH494" t="inlineStr"/>
+      <c r="AI494" t="inlineStr"/>
+      <c r="AJ494" t="inlineStr"/>
+      <c r="AK494" t="inlineStr"/>
+      <c r="AL494" t="inlineStr"/>
+      <c r="AM494" t="inlineStr"/>
+      <c r="AN494" t="inlineStr"/>
+      <c r="AO494" t="inlineStr"/>
+      <c r="AP494" t="inlineStr"/>
+      <c r="AQ494" t="inlineStr"/>
+      <c r="AR494" t="inlineStr"/>
+      <c r="AS494" t="inlineStr"/>
+      <c r="AT494" t="inlineStr"/>
+      <c r="AU494" t="inlineStr"/>
+      <c r="AV494" t="inlineStr"/>
+      <c r="AW494" t="inlineStr"/>
+      <c r="AX494" t="inlineStr"/>
+      <c r="AY494" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ494" t="n">
+        <v>483</v>
+      </c>
+      <c r="BA494" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB494" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC494" t="inlineStr"/>
+      <c r="BD494" t="inlineStr"/>
+      <c r="BE494" t="inlineStr"/>
+      <c r="BF494" t="inlineStr"/>
+      <c r="BG494" t="inlineStr"/>
+      <c r="BH494" t="inlineStr"/>
+      <c r="BI494" t="inlineStr"/>
+      <c r="BJ494" t="inlineStr"/>
+      <c r="BK494" t="inlineStr"/>
+      <c r="BL494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>KGmbFEdf</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>01.09.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Kitchen A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Bramall Lane
+ (Sheffield)</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>32 050</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>26 914</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>Sheffield Utd</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr"/>
+      <c r="N495" t="inlineStr"/>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T495" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U495" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V495" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W495" t="inlineStr"/>
+      <c r="X495" t="inlineStr"/>
+      <c r="Y495" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z495" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA495" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB495" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC495" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD495" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AE495" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF495" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG495" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH495" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI495" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ495" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK495" t="inlineStr"/>
+      <c r="AL495" t="inlineStr"/>
+      <c r="AM495" t="inlineStr"/>
+      <c r="AN495" t="inlineStr"/>
+      <c r="AO495" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AP495" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="AQ495" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AR495" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AS495" t="inlineStr"/>
+      <c r="AT495" t="inlineStr"/>
+      <c r="AU495" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="AV495" t="inlineStr">
+        <is>
+          <t>wilder chris</t>
+        </is>
+      </c>
+      <c r="AW495" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="AX495" t="inlineStr">
+        <is>
+          <t>cleverley tom</t>
+        </is>
+      </c>
+      <c r="AY495" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ495" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA495" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB495" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC495" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BD495" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BE495" t="inlineStr"/>
+      <c r="BF495" t="inlineStr"/>
+      <c r="BG495" t="inlineStr"/>
+      <c r="BH495" t="inlineStr"/>
+      <c r="BI495" t="inlineStr"/>
+      <c r="BJ495" t="inlineStr"/>
+      <c r="BK495" t="inlineStr"/>
+      <c r="BL495" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
